--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R173c94c5ce454940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R8afd7d03e6824d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rc920da1da1344e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R4ffc202d012f45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R1b7a80c8467e4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="Rc60b1677aee049bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R7dbfbd481c2d4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R10f6ff3d37fd4940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1a26450581f246f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R4d0b084c839c4e8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rc59934df13954711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R08c6c8a4f1db42c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R60f611ebca5b4bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R7b2704b8b7984ee7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="5">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FFB4C6E7"/>
@@ -154,6 +160,7 @@
       <x:bottom style="thin">
         <x:color rgb="FFB4C6E7"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -168,6 +175,7 @@
       <x:bottom style="thin">
         <x:color rgb="FFA8C8C2"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -182,6 +190,7 @@
       <x:bottom style="thin">
         <x:color rgb="FFE6B8AF"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -196,6 +205,7 @@
       <x:bottom style="thin">
         <x:color rgb="FFD9D9D9"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
@@ -774,7 +784,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3071f7cb5fde4070"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc29d605b2bf84b29"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -804,7 +814,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22404c6116df4d58"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R896e10b5f35a4783"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1124,49 +1134,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-09-29；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1220,31 +1230,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>67.04990806519942</x:v>
+        <x:v>59.80311682482056</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.66753187252903</x:v>
+        <x:v>46.3406640711772</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>72.99356435513207</x:v>
+        <x:v>83.45640641965412</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.721971353191776</x:v>
+        <x:v>55.18861521182057</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>63.872408828311634</x:v>
+        <x:v>63.80057367264977</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1269,7 +1279,7 @@
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="100" t="str">
         <x:f>IF(A6&gt;=65,"高压",IF(A6&gt;=55,"偏紧",IF(A6&gt;=45,"中性",IF(A6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="B8" s="100"/>
       <x:c r="C8" s="100"/>
@@ -1287,7 +1297,7 @@
       <x:c r="I8" s="100"/>
       <x:c r="J8" s="100" t="str">
         <x:f>IF(J6&gt;=65,"高压",IF(J6&gt;=55,"偏紧",IF(J6&gt;=45,"中性",IF(J6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="K8" s="100"/>
       <x:c r="L8" s="100"/>
@@ -1349,7 +1359,7 @@
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="104" t="str">
         <x:f>'因子引擎'!$B$53</x:f>
-        <x:v>政策重定价 + 期限溢价冲击</x:v>
+        <x:v>混合状态</x:v>
       </x:c>
       <x:c r="B11" s="104"/>
       <x:c r="C11" s="104"/>
@@ -1408,7 +1418,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.6866219151954133</x:v>
+        <x:v>0.49180612268419316</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1418,7 +1428,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.31337808480458673</x:v>
+        <x:v>0.5081938773158068</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1455,7 +1465,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.5800000000000001</x:v>
+        <x:v>0.33999999999999986</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1502,7 +1512,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.792749194213457</x:v>
+        <x:v>0.984785831461947</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1512,7 +1522,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.06591862656869607</x:v>
+        <x:v>0.28140627728938594</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1549,7 +1559,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.3900000000000001</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1559,7 +1569,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>16.07</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1596,7 +1606,7 @@
       </x:c>
       <x:c r="J16" s="39" t="n">
         <x:f>'因子引擎'!$E$37</x:f>
-        <x:v>-0.555</x:v>
+        <x:v>-0.494</x:v>
       </x:c>
       <x:c r="K16" s="39" t="str">
         <x:v>仍偏宽松</x:v>
@@ -1654,11 +1664,11 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>67.04990806519942</x:v>
+        <x:v>59.80311682482056</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
@@ -1667,7 +1677,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.66753187252903</x:v>
+        <x:v>46.3406640711772</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1680,7 +1690,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>72.99356435513207</x:v>
+        <x:v>83.45640641965412</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1693,11 +1703,11 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.721971353191776</x:v>
+        <x:v>55.18861521182057</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
@@ -1706,7 +1716,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>63.872408828311634</x:v>
+        <x:v>63.80057367264977</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1755,7 +1765,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>38.27140451588909</x:v>
+        <x:v>37.57067571760262</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1768,7 +1778,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>38.41416569151566</x:v>
+        <x:v>37.558513090994715</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1781,7 +1791,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>39.13863232150779</x:v>
+        <x:v>39.520156477787054</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1794,7 +1804,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>39.595222570100674</x:v>
+        <x:v>39.6910639449352</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1807,7 +1817,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>39.59932565123882</x:v>
+        <x:v>39.14271807626149</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1820,7 +1830,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>39.51929700197569</x:v>
+        <x:v>38.27839597763003</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1833,7 +1843,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>37.429970137586736</x:v>
+        <x:v>36.53524218843517</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1846,7 +1856,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>43.67190940147365</x:v>
+        <x:v>41.84245579925653</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1859,7 +1869,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>37.67000689888785</x:v>
+        <x:v>35.96643189365785</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1872,7 +1882,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>61.35251938451624</x:v>
+        <x:v>60.90314178704433</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2098,7 +2108,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28b2db1c345744b7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9156ba05c7b842ae"/>
 </x:worksheet>
 </file>
 
@@ -2222,49 +2232,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-09-29。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2328,27 +2338,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>1.04</x:v>
+        <x:v>0.8899999999999997</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.1216499665998664</x:v>
+        <x:v>-0.11668218085106385</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0934728639214981</x:v>
+        <x:v>1.0933456087386109</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>1.0623491491447408</x:v>
+        <x:v>0.9207355595569359</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>71.24698298289482</x:v>
+        <x:v>68.41471119113872</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2377,27 +2387,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.5800000000000001</x:v>
+        <x:v>0.33999999999999986</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.05705410821643279</x:v>
+        <x:v>0.06175531914893609</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0524426987263638</x:v>
+        <x:v>1.0574818398543389</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.49688775685025094</x:v>
+        <x:v>0.2631200559334335</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>59.93775513700502</x:v>
+        <x:v>55.26240111866867</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2426,27 +2436,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E7" s="56" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.03519313304721038</x:v>
+        <x:v>0.0359924026590694</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18340417915064805</x:v>
+        <x:v>0.18349001911725</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>1.171221222698243</x:v>
+        <x:v>-0.19615455288644493</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>73.42442445396486</x:v>
+        <x:v>46.0769089422711</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2491,11 +2501,11 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>67.04990806519942</x:v>
+        <x:v>59.80311682482056</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="L8" s="64"/>
       <x:c r="M8" s="64"/>
@@ -2533,27 +2543,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.34</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.344672897196265</x:v>
+        <x:v>2.3447707641196045</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.556733416763447</x:v>
+        <x:v>0.5554382649457756</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>-0.008393419643158508</x:v>
+        <x:v>0.04542221426328738</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>49.83213160713683</x:v>
+        <x:v>50.908444285265745</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2582,27 +2592,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>-0.03000000000000025</x:v>
+        <x:v>-0.08999999999999986</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.006074766355140195</x:v>
+        <x:v>0.007508305647840539</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6947172161666386</x:v>
+        <x:v>0.6957560158617611</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>-0.05192726697374282</x:v>
+        <x:v>-0.14014726919330614</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>48.96145466052514</x:v>
+        <x:v>47.197054616133876</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2631,27 +2641,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.36</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.160987983978639</x:v>
+        <x:v>2.1618737541528246</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.460931021595581</x:v>
+        <x:v>0.46004026478298776</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.43176095054841673</x:v>
+        <x:v>0.36545984931663483</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>58.635219010968335</x:v>
+        <x:v>57.309196986332694</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2696,7 +2706,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>52.16832089697219</x:v>
+        <x:v>51.529683711389666</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -2738,27 +2748,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E15" s="56" t="n">
-        <x:v>3.085745494265435</x:v>
+        <x:v>3.0245231607629375</x:v>
       </x:c>
       <x:c r="F15" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G15" s="56" t="n">
-        <x:v>4.304672044722189</x:v>
+        <x:v>4.286117534594615</x:v>
       </x:c>
       <x:c r="H15" s="56" t="n">
-        <x:v>0.8463168288520321</x:v>
+        <x:v>0.8540343631541617</x:v>
       </x:c>
       <x:c r="I15" s="58" t="n">
         <x:f>IFERROR(C15*(E15-G15)/H15,"")</x:f>
-        <x:v>-1.4402721402930625</x:v>
+        <x:v>-1.4772173442439656</x:v>
       </x:c>
       <x:c r="J15" s="58" t="n">
         <x:f>IF(I15="","",MAX(0,MIN(100,50+20*I15)))</x:f>
-        <x:v>21.19455719413875</x:v>
+        <x:v>20.45565311512069</x:v>
       </x:c>
       <x:c r="K15" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L15" s="54" t="n">
         <x:v>5</x:v>
@@ -2787,27 +2797,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E16" s="56" t="n">
-        <x:v>4.1</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="F16" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G16" s="56" t="n">
-        <x:v>4.788059701492538</x:v>
+        <x:v>4.776470588235295</x:v>
       </x:c>
       <x:c r="H16" s="56" t="n">
-        <x:v>1.0265450126752333</x:v>
+        <x:v>1.0237650218763872</x:v>
       </x:c>
       <x:c r="I16" s="58" t="n">
         <x:f>IFERROR(C16*(E16-G16)/H16,"")</x:f>
-        <x:v>-0.6702674437036296</x:v>
+        <x:v>-0.8561247644785456</x:v>
       </x:c>
       <x:c r="J16" s="58" t="n">
         <x:f>IF(I16="","",MAX(0,MIN(100,50+20*I16)))</x:f>
-        <x:v>36.59465112592741</x:v>
+        <x:v>32.87750471042909</x:v>
       </x:c>
       <x:c r="K16" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L16" s="54" t="n">
         <x:v>5</x:v>
@@ -2836,27 +2846,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E17" s="56" t="n">
-        <x:v>4.1</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="F17" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G17" s="56" t="n">
-        <x:v>4.127941176470588</x:v>
+        <x:v>4.128985507246377</x:v>
       </x:c>
       <x:c r="H17" s="56" t="n">
-        <x:v>0.8688378905585538</x:v>
+        <x:v>0.862469342895114</x:v>
       </x:c>
       <x:c r="I17" s="58" t="n">
         <x:f>IFERROR(C17*(E17-G17)/H17,"")</x:f>
-        <x:v>0.03215925177092117</x:v>
+        <x:v>-0.08233857045311783</x:v>
       </x:c>
       <x:c r="J17" s="58" t="n">
         <x:f>IF(I17="","",MAX(0,MIN(100,50+20*I17)))</x:f>
-        <x:v>50.643185035418426</x:v>
+        <x:v>48.35322859093765</x:v>
       </x:c>
       <x:c r="K17" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L17" s="54" t="n">
         <x:v>5</x:v>
@@ -2934,27 +2944,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E19" s="56" t="n">
-        <x:v>202250</x:v>
+        <x:v>198000</x:v>
       </x:c>
       <x:c r="F19" s="57" t="str">
         <x:v>人</x:v>
       </x:c>
       <x:c r="G19" s="56" t="n">
-        <x:v>265131.27090301004</x:v>
+        <x:v>264694.35215946846</x:v>
       </x:c>
       <x:c r="H19" s="56" t="n">
-        <x:v>129858.89069941026</x:v>
+        <x:v>129535.93781133559</x:v>
       </x:c>
       <x:c r="I19" s="58" t="n">
         <x:f>IFERROR(C19*(E19-G19)/H19,"")</x:f>
-        <x:v>0.4842276917994311</x:v>
+        <x:v>0.5148714193632223</x:v>
       </x:c>
       <x:c r="J19" s="58" t="n">
         <x:f>IF(I19="","",MAX(0,MIN(100,50+20*I19)))</x:f>
-        <x:v>59.68455383598862</x:v>
+        <x:v>60.297428387264446</x:v>
       </x:c>
       <x:c r="K19" s="54" t="str">
-        <x:v>2026-09-19</x:v>
+        <x:v>2026-10-03</x:v>
       </x:c>
       <x:c r="L19" s="54" t="n">
         <x:v>5</x:v>
@@ -2999,7 +3009,7 @@
       </x:c>
       <x:c r="J20" s="63" t="n">
         <x:f>SUMPRODUCT(D15:D19,J15:J19)/SUM(D15:D19)</x:f>
-        <x:v>36.90120306873667</x:v>
+        <x:v>35.53562816112684</x:v>
       </x:c>
       <x:c r="K20" s="64" t="str">
         <x:f>IF(J20&gt;=65,"高压",IF(J20&gt;=55,"偏紧",IF(J20&gt;=45,"中性",IF(J20&gt;=35,"偏松","宽松"))))</x:f>
@@ -3090,27 +3100,27 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="E23" s="56" t="n">
-        <x:v>36.63548752834467</x:v>
+        <x:v>19.641969169567375</x:v>
       </x:c>
       <x:c r="F23" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G23" s="56" t="n">
-        <x:v>-0.1652120921194438</x:v>
+        <x:v>0.03865234184929262</x:v>
       </x:c>
       <x:c r="H23" s="56" t="n">
-        <x:v>28.669158522884732</x:v>
+        <x:v>28.69987590646968</x:v>
       </x:c>
       <x:c r="I23" s="58" t="n">
         <x:f>IFERROR(C23*(E23-G23)/H23,"")</x:f>
-        <x:v>1.2836337554549604</x:v>
+        <x:v>0.6830453515410148</x:v>
       </x:c>
       <x:c r="J23" s="58" t="n">
         <x:f>IF(I23="","",MAX(0,MIN(100,50+20*I23)))</x:f>
-        <x:v>75.6726751090992</x:v>
+        <x:v>63.6609070308203</x:v>
       </x:c>
       <x:c r="K23" s="54" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="L23" s="54" t="n">
         <x:v>5</x:v>
@@ -3155,11 +3165,11 @@
       </x:c>
       <x:c r="J24" s="63" t="n">
         <x:f>SUMPRODUCT(D22:D23,J22:J23)/SUM(D22:D23)</x:f>
-        <x:v>61.38183197416857</x:v>
+        <x:v>53.57418272328729</x:v>
       </x:c>
       <x:c r="K24" s="64" t="str">
         <x:f>IF(J24&gt;=65,"高压",IF(J24&gt;=55,"偏紧",IF(J24&gt;=45,"中性",IF(J24&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="L24" s="64"/>
       <x:c r="M24" s="64"/>
@@ -3213,7 +3223,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>48.66753187252903</x:v>
+        <x:v>46.3406640711772</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3255,27 +3265,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.792749194213457</x:v>
+        <x:v>0.984785831461947</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.050209498814714856</x:v>
+        <x:v>-0.05308498660245277</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5412637002342298</x:v>
+        <x:v>0.5465658488117167</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.5573900349559462</x:v>
+        <x:v>1.898894379004514</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>81.14780069911893</x:v>
+        <x:v>87.97788758009028</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3304,27 +3314,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.06591862656869607</x:v>
+        <x:v>0.28140627728938594</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.021131053576928755</x:v>
+        <x:v>0.02207740418154717</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.2257999874502728</x:v>
+        <x:v>0.22642596797343048</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.19835064429146942</x:v>
+        <x:v>1.1453141855984876</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>53.96701288582939</x:v>
+        <x:v>72.90628371196975</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3369,7 +3379,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>72.99356435513207</x:v>
+        <x:v>83.45640641965412</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3417,21 +3427,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04571810287241148</x:v>
+        <x:v>0.04935505319148935</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5038614614678806</x:v>
+        <x:v>0.5089432219753734</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.8222138996713039</x:v>
+        <x:v>0.8068580719371103</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>66.44427799342608</x:v>
+        <x:v>66.13716143874221</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3460,27 +3470,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.3900000000000001</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.04137128072445022</x:v>
+        <x:v>-0.0381524547803618</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5331927327059182</x:v>
+        <x:v>0.5340727574341289</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.809034434012762</x:v>
+        <x:v>0.7829503545346731</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>66.18068868025524</x:v>
+        <x:v>65.65900709069346</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3509,27 +3519,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.029999999999999916</x:v>
+        <x:v>0.009999999999999898</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.012690815006468327</x:v>
+        <x:v>-0.012661498708010355</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.1543312629922082</x:v>
+        <x:v>0.1542201401680597</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.2766180628523956</x:v>
+        <x:v>0.1469425373580593</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>55.53236125704791</x:v>
+        <x:v>52.93885074716118</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3558,27 +3568,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>16.07</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.86704074816298</x:v>
+        <x:v>18.85216090425531</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.601072697974099</x:v>
+        <x:v>5.592373708660112</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.49937590511450913</x:v>
+        <x:v>-0.6745187465590688</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>40.01248189770982</x:v>
+        <x:v>36.50962506881862</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3607,27 +3617,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E36" s="56" t="n">
-        <x:v>1.3323182978393744</x:v>
+        <x:v>2.8047008127161766</x:v>
       </x:c>
       <x:c r="F36" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G36" s="56" t="n">
-        <x:v>-3.883202831496552</x:v>
+        <x:v>-3.8615249593235617</x:v>
       </x:c>
       <x:c r="H36" s="56" t="n">
-        <x:v>19.616322888282035</x:v>
+        <x:v>19.585629739935477</x:v>
       </x:c>
       <x:c r="I36" s="58" t="n">
         <x:f>IFERROR(C36*(E36-G36)/H36,"")</x:f>
-        <x:v>0.26587659466247154</x:v>
+        <x:v>0.3403631060403013</x:v>
       </x:c>
       <x:c r="J36" s="58" t="n">
         <x:f>IF(I36="","",MAX(0,MIN(100,50+20*I36)))</x:f>
-        <x:v>55.31753189324943</x:v>
+        <x:v>56.80726212080603</x:v>
       </x:c>
       <x:c r="K36" s="54" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>2026-10-02</x:v>
       </x:c>
       <x:c r="L36" s="54" t="n">
         <x:v>5</x:v>
@@ -3656,27 +3666,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E37" s="56" t="n">
-        <x:v>-0.555</x:v>
+        <x:v>-0.494</x:v>
       </x:c>
       <x:c r="F37" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G37" s="56" t="n">
-        <x:v>-0.4300602006688966</x:v>
+        <x:v>-0.43021926910299024</x:v>
       </x:c>
       <x:c r="H37" s="56" t="n">
-        <x:v>0.15126041942465757</x:v>
+        <x:v>0.15079438018086308</x:v>
       </x:c>
       <x:c r="I37" s="58" t="n">
         <x:f>IFERROR(C37*(E37-G37)/H37,"")</x:f>
-        <x:v>-0.8259913585214911</x:v>
+        <x:v>-0.422964906387831</x:v>
       </x:c>
       <x:c r="J37" s="58" t="n">
         <x:f>IF(I37="","",MAX(0,MIN(100,50+20*I37)))</x:f>
-        <x:v>33.48017282957018</x:v>
+        <x:v>41.54070187224338</x:v>
       </x:c>
       <x:c r="K37" s="54" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-10-02</x:v>
       </x:c>
       <x:c r="L37" s="54" t="n">
         <x:v>5</x:v>
@@ -3721,11 +3731,11 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>54.721971353191776</x:v>
+        <x:v>55.18861521182057</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="L38" s="64"/>
       <x:c r="M38" s="64"/>
@@ -3829,7 +3839,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>67.04990806519942</x:v>
+        <x:v>59.80311682482056</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3855,7 +3865,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>48.66753187252903</x:v>
+        <x:v>46.3406640711772</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3881,7 +3891,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>72.99356435513207</x:v>
+        <x:v>83.45640641965412</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3907,7 +3917,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>54.721971353191776</x:v>
+        <x:v>55.18861521182057</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3933,7 +3943,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>62.39917328474457</x:v>
+        <x:v>62.187245239495454</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3959,7 +3969,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>63.872408828311634</x:v>
+        <x:v>63.80057367264977</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3985,7 +3995,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>57.78167346150877</x:v>
+        <x:v>60.12977211791329</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4011,7 +4021,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.6866219151954133</x:v>
+        <x:v>0.49180612268419316</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4037,7 +4047,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.31337808480458673</x:v>
+        <x:v>0.5081938773158068</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4115,7 +4125,7 @@
       </x:c>
       <x:c r="B53" s="68" t="str">
         <x:f>IF(AND(B42&gt;=60,B44&gt;=60,B43&lt;60),"政策重定价 + 期限溢价冲击",IF(AND(B46&gt;=65,B45&gt;=60),"全面收紧传导",IF(AND(B43&gt;=60,B44&gt;=60),"通胀与期限溢价共振",IF(AND(B42&gt;=60,B43&lt;55,B45&lt;55),"政策独涨/预防性加息",IF(AND(B46&lt;=40,B45&lt;=45),"宽松传导","混合状态")))))</x:f>
-        <x:v>政策重定价 + 期限溢价冲击</x:v>
+        <x:v>混合状态</x:v>
       </x:c>
       <x:c r="C53" s="68" t="str">
         <x:v>规则优先于主观叙事</x:v>
@@ -4322,7 +4332,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>38.27140451588909</x:v>
+        <x:v>37.57067571760262</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4356,7 +4366,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>38.41416569151566</x:v>
+        <x:v>37.558513090994715</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4390,7 +4400,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>39.13863232150779</x:v>
+        <x:v>39.520156477787054</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4424,7 +4434,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>39.595222570100674</x:v>
+        <x:v>39.6910639449352</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4458,7 +4468,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>39.59932565123882</x:v>
+        <x:v>39.14271807626149</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4492,7 +4502,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>39.51929700197569</x:v>
+        <x:v>38.27839597763003</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4526,7 +4536,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>37.429970137586736</x:v>
+        <x:v>36.53524218843517</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4560,7 +4570,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>43.67190940147365</x:v>
+        <x:v>41.84245579925653</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4594,7 +4604,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>37.67000689888785</x:v>
+        <x:v>35.96643189365785</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4628,7 +4638,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>61.35251938451624</x:v>
+        <x:v>60.90314178704433</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4832,43 +4842,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>67.04990806519942</x:v>
+        <x:v>59.80311682482056</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.66753187252903</x:v>
+        <x:v>46.3406640711772</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>72.99356435513207</x:v>
+        <x:v>83.45640641965412</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.721971353191776</x:v>
+        <x:v>55.18861521182057</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>63.872408828311634</x:v>
+        <x:v>63.80057367264977</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>38.27140451588909</x:v>
+        <x:v>37.57067571760262</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>38.41416569151566</x:v>
+        <x:v>37.558513090994715</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>39.595222570100674</x:v>
+        <x:v>39.6910639449352</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>39.51929700197569</x:v>
+        <x:v>38.27839597763003</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>61.35251938451624</x:v>
+        <x:v>60.90314178704433</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7238,7 +7248,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>63.872408828311634</x:v>
+        <x:v>63.80057367264977</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7261,7 +7271,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>37.429970137586736</x:v>
+        <x:v>35.96643189365785</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R10f6ff3d37fd4940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1a26450581f246f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R4d0b084c839c4e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rc59934df13954711"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R08c6c8a4f1db42c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R60f611ebca5b4bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R7b2704b8b7984ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Re05b83b34c584605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R983f4a27f05c43fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rb1f189a8869e4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rb72fdae4d6eb4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Ra20be21a83a04095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R36c87f8980104214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Re60d5d3cfe6f42da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -492,6 +492,7 @@
               <a:srgbClr val="2F75B5"/>
             </a:solidFill>
           </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>'模型总览'!$A$20:$A$24</c:f>
@@ -651,6 +652,7 @@
               <a:srgbClr val="1B7F79"/>
             </a:solidFill>
           </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>'模型总览'!$A$29:$A$38</c:f>
@@ -784,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc29d605b2bf84b29"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0dccfbb069474e37"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -814,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R896e10b5f35a4783"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8e618c60475946a3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1134,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-08；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1230,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>59.80311682482056</x:v>
+        <x:v>58.49863697160385</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.3406640711772</x:v>
+        <x:v>46.24742809324514</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>83.45640641965412</x:v>
+        <x:v>78.62746550273289</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>55.18861521182057</x:v>
+        <x:v>54.63454401541005</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>63.80057367264977</x:v>
+        <x:v>61.64550403377792</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1297,7 +1299,7 @@
       <x:c r="I8" s="100"/>
       <x:c r="J8" s="100" t="str">
         <x:f>IF(J6&gt;=65,"高压",IF(J6&gt;=55,"偏紧",IF(J6&gt;=45,"中性",IF(J6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="K8" s="100"/>
       <x:c r="L8" s="100"/>
@@ -1418,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.49180612268419316</x:v>
+        <x:v>0.5006203645437454</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1428,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.5081938773158068</x:v>
+        <x:v>0.49937963545625463</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1465,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.33999999999999986</x:v>
+        <x:v>0.1900000000000004</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1475,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.45999999999999996</x:v>
+        <x:v>0.3200000000000003</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1512,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.984785831461947</x:v>
+        <x:v>0.919782824415004</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1522,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.28140627728938594</x:v>
+        <x:v>0.163432003121593</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1559,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>0.44999999999999973</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1569,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>15.08</x:v>
+        <x:v>15.41</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1664,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>59.80311682482056</x:v>
+        <x:v>58.49863697160385</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1677,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.3406640711772</x:v>
+        <x:v>46.24742809324514</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1690,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>83.45640641965412</x:v>
+        <x:v>78.62746550273289</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1703,11 +1705,11 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>55.18861521182057</x:v>
+        <x:v>54.63454401541005</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
@@ -1716,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>63.80057367264977</x:v>
+        <x:v>61.64550403377792</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1765,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>37.57067571760262</x:v>
+        <x:v>39.43376672454271</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1778,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>37.558513090994715</x:v>
+        <x:v>39.39747884308603</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1791,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>39.520156477787054</x:v>
+        <x:v>41.01994163653421</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1804,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>39.6910639449352</x:v>
+        <x:v>41.163056190467316</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1817,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>39.14271807626149</x:v>
+        <x:v>40.72817794569087</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1830,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>38.27839597763003</x:v>
+        <x:v>39.69489813856764</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1843,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>36.53524218843517</x:v>
+        <x:v>38.32619706160781</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1856,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>41.84245579925653</x:v>
+        <x:v>42.60696729044399</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1869,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>35.96643189365785</x:v>
+        <x:v>38.108496431809755</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1882,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>60.90314178704433</x:v>
+        <x:v>59.32769951131025</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2108,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9156ba05c7b842ae"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6619c35bb0924bdc"/>
 </x:worksheet>
 </file>
 
@@ -2232,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-08。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2338,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.8899999999999997</x:v>
+        <x:v>0.8700000000000001</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11668218085106385</x:v>
+        <x:v>-0.11602657807308972</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0933456087386109</x:v>
+        <x:v>1.09327794948268</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9207355595569359</x:v>
+        <x:v>0.9018992640797889</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>68.41471119113872</x:v>
+        <x:v>68.03798528159578</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2387,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.33999999999999986</x:v>
+        <x:v>0.1900000000000004</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.06175531914893609</x:v>
+        <x:v>0.061840531561461715</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0574818398543389</x:v>
+        <x:v>1.0571353936513326</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.2631200559334335</x:v>
+        <x:v>0.12123278551470824</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>55.26240111866867</x:v>
+        <x:v>52.42465571029417</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2442,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.0359924026590694</x:v>
+        <x:v>0.0359753203607025</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18349001911725</x:v>
+        <x:v>0.18344812608793803</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.19615455288644493</x:v>
+        <x:v>-0.196106229743973</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.0769089422711</x:v>
+        <x:v>46.07787540512054</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2501,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>59.80311682482056</x:v>
+        <x:v>58.49863697160385</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2543,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.37</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.3447707641196045</x:v>
+        <x:v>2.3447675962815437</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5554382649457756</x:v>
+        <x:v>0.5552537169066695</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>0.04542221426328738</x:v>
+        <x:v>-0.008586338346556718</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>50.908444285265745</x:v>
+        <x:v>49.82827323306886</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2592,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>-0.08999999999999986</x:v>
+        <x:v>-0.06000000000000005</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.007508305647840539</x:v>
+        <x:v>0.007463479415670658</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6957560158617611</x:v>
+        <x:v>0.6955270047093637</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>-0.14014726919330614</x:v>
+        <x:v>-0.0969962042578941</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>47.197054616133876</x:v>
+        <x:v>48.060075914842116</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2641,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.33</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.1618737541528246</x:v>
+        <x:v>2.1619787516600275</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.46004026478298776</x:v>
+        <x:v>0.45990545274200617</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.36545984931663483</x:v>
+        <x:v>0.34359507459159816</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>57.309196986332694</x:v>
+        <x:v>56.87190149183196</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2706,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>51.529683711389666</x:v>
+        <x:v>51.32249264931842</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -3223,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>46.3406640711772</x:v>
+        <x:v>46.24742809324514</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3265,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.984785831461947</x:v>
+        <x:v>0.919782824415004</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.05308498660245277</x:v>
+        <x:v>-0.052410788535219605</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5465658488117167</x:v>
+        <x:v>0.5469762024916136</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.898894379004514</x:v>
+        <x:v>1.7773965458124836</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>87.97788758009028</x:v>
+        <x:v>85.54793091624967</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3314,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.28140627728938594</x:v>
+        <x:v>0.163432003121593</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.02207740418154717</x:v>
+        <x:v>0.02217536301657146</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22642596797343048</x:v>
+        <x:v>0.22637802898667123</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>1.1453141855984876</x:v>
+        <x:v>0.6239856435596871</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>72.90628371196975</x:v>
+        <x:v>62.47971287119374</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3379,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>83.45640641965412</x:v>
+        <x:v>78.62746550273289</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3421,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.45999999999999996</x:v>
+        <x:v>0.3200000000000003</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04935505319148935</x:v>
+        <x:v>0.04953488372093022</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5089432219753734</x:v>
+        <x:v>0.5088218259315177</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.8068580719371103</x:v>
+        <x:v>0.5315517190795034</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>66.13716143874221</x:v>
+        <x:v>60.63103438159007</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3470,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.3799999999999999</x:v>
+        <x:v>0.44999999999999973</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.0381524547803618</x:v>
+        <x:v>-0.03713178294573645</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5340727574341289</x:v>
+        <x:v>0.534250006351034</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.7829503545346731</x:v>
+        <x:v>0.91180491746342</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>65.65900709069346</x:v>
+        <x:v>68.2360983492684</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3519,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.009999999999999898</x:v>
+        <x:v>0.019999999999999907</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.012661498708010355</x:v>
+        <x:v>-0.012622739018087878</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.1542201401680597</x:v>
+        <x:v>0.1542245797815252</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.1469425373580593</x:v>
+        <x:v>0.2115274949317496</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>52.93885074716118</x:v>
+        <x:v>54.23054989863499</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3568,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>15.08</x:v>
+        <x:v>15.41</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.85216090425531</x:v>
+        <x:v>18.849873754152814</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.592373708660112</x:v>
+        <x:v>5.591218304181021</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.6745187465590688</x:v>
+        <x:v>-0.615227946220689</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>36.50962506881862</x:v>
+        <x:v>37.69544107558622</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3731,11 +3733,11 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>55.18861521182057</x:v>
+        <x:v>54.63454401541005</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="L38" s="64"/>
       <x:c r="M38" s="64"/>
@@ -3839,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>59.80311682482056</x:v>
+        <x:v>58.49863697160385</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3865,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>46.3406640711772</x:v>
+        <x:v>46.24742809324514</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3891,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>83.45640641965412</x:v>
+        <x:v>78.62746550273289</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3917,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>55.18861521182057</x:v>
+        <x:v>54.63454401541005</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3943,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>62.187245239495454</x:v>
+        <x:v>60.24936242351701</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3969,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>63.80057367264977</x:v>
+        <x:v>61.64550403377792</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3995,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>60.12977211791329</x:v>
+        <x:v>58.47757409274094</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4021,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.49180612268419316</x:v>
+        <x:v>0.5006203645437454</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4047,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.5081938773158068</x:v>
+        <x:v>0.49937963545625463</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4332,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>37.57067571760262</x:v>
+        <x:v>39.43376672454271</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4366,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>37.558513090994715</x:v>
+        <x:v>39.39747884308603</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4400,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>39.520156477787054</x:v>
+        <x:v>41.01994163653421</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4434,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>39.6910639449352</x:v>
+        <x:v>41.163056190467316</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4468,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>39.14271807626149</x:v>
+        <x:v>40.72817794569087</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4502,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>38.27839597763003</x:v>
+        <x:v>39.69489813856764</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4536,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>36.53524218843517</x:v>
+        <x:v>38.32619706160781</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4570,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>41.84245579925653</x:v>
+        <x:v>42.60696729044399</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4604,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>35.96643189365785</x:v>
+        <x:v>38.108496431809755</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4638,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>60.90314178704433</x:v>
+        <x:v>59.32769951131025</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4842,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>59.80311682482056</x:v>
+        <x:v>58.49863697160385</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.3406640711772</x:v>
+        <x:v>46.24742809324514</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>83.45640641965412</x:v>
+        <x:v>78.62746550273289</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>55.18861521182057</x:v>
+        <x:v>54.63454401541005</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>63.80057367264977</x:v>
+        <x:v>61.64550403377792</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>37.57067571760262</x:v>
+        <x:v>39.43376672454271</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>37.558513090994715</x:v>
+        <x:v>39.39747884308603</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>39.6910639449352</x:v>
+        <x:v>41.163056190467316</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>38.27839597763003</x:v>
+        <x:v>39.69489813856764</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>60.90314178704433</x:v>
+        <x:v>59.32769951131025</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7248,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>63.80057367264977</x:v>
+        <x:v>61.64550403377792</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7271,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>35.96643189365785</x:v>
+        <x:v>38.108496431809755</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Re05b83b34c584605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R983f4a27f05c43fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rb1f189a8869e4b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rb72fdae4d6eb4f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Ra20be21a83a04095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R36c87f8980104214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Re60d5d3cfe6f42da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R26678c6ccb234df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1c35a216f42844a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rb5385ff3bb6d4afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R86aaa2e817154065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rde867f4881d94cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="Rcecdce5dbb1240bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Reca5f147a7d841af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0dccfbb069474e37"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0d4c80a5a954c2d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8e618c60475946a3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R869db1e30fe64c03"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-09；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.49863697160385</x:v>
+        <x:v>58.753822467813286</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.24742809324514</x:v>
+        <x:v>46.17802682129179</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.62746550273289</x:v>
+        <x:v>78.80996983584953</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.63454401541005</x:v>
+        <x:v>54.16995501879927</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.64550403377792</x:v>
+        <x:v>61.6278211560705</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.5006203645437454</x:v>
+        <x:v>0.5113509562785417</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.49937963545625463</x:v>
+        <x:v>0.48864904372145834</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.1900000000000004</x:v>
+        <x:v>0.16999999999999993</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.3200000000000003</x:v>
+        <x:v>0.31000000000000005</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.919782824415004</x:v>
+        <x:v>0.902297147892582</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.163432003121593</x:v>
+        <x:v>0.18858293392940095</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.44999999999999973</x:v>
+        <x:v>0.3999999999999999</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>15.41</x:v>
+        <x:v>15.21</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1666,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.49863697160385</x:v>
+        <x:v>58.753822467813286</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.24742809324514</x:v>
+        <x:v>46.17802682129179</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.62746550273289</x:v>
+        <x:v>78.80996983584953</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,7 +1705,7 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.63454401541005</x:v>
+        <x:v>54.16995501879927</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.64550403377792</x:v>
+        <x:v>61.6278211560705</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>39.43376672454271</x:v>
+        <x:v>39.43805842029876</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>39.39747884308603</x:v>
+        <x:v>39.429098284164795</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>41.01994163653421</x:v>
+        <x:v>41.092885689077264</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>41.163056190467316</x:v>
+        <x:v>41.26265855755927</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>40.72817794569087</x:v>
+        <x:v>40.81583562531746</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>39.69489813856764</x:v>
+        <x:v>39.66673564542544</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>38.32619706160781</x:v>
+        <x:v>38.38522070865495</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>42.60696729044399</x:v>
+        <x:v>42.59663638524673</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>38.108496431809755</x:v>
+        <x:v>38.07732085483303</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>59.32769951131025</x:v>
+        <x:v>59.28608705429261</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6619c35bb0924bdc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1811f571040414f"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-09。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.8700000000000001</x:v>
+        <x:v>0.9199999999999999</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11602657807308972</x:v>
+        <x:v>-0.11533864541832672</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.09327794948268</x:v>
+        <x:v>1.0932406875238847</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9018992640797889</x:v>
+        <x:v>0.9470363271635067</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>68.03798528159578</x:v>
+        <x:v>68.94072654327013</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.1900000000000004</x:v>
+        <x:v>0.16999999999999993</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.061840531561461715</x:v>
+        <x:v>0.06191235059760948</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0571353936513326</x:v>
+        <x:v>1.0567878027714774</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.12123278551470824</x:v>
+        <x:v>0.10227942555631823</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>52.42465571029417</x:v>
+        <x:v>52.04558851112637</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.0359753203607025</x:v>
+        <x:v>0.03590715300805313</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18344812608793803</x:v>
+        <x:v>0.18328083985203292</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.196106229743973</x:v>
+        <x:v>-0.1959132937029416</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.07787540512054</x:v>
+        <x:v>46.08173412594117</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>58.49863697160385</x:v>
+        <x:v>58.753822467813286</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.34</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.3447675962815437</x:v>
+        <x:v>2.3432029177718863</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5552537169066695</x:v>
+        <x:v>0.5581608045007573</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>-0.008586338346556718</x:v>
+        <x:v>-0.023654326254054066</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>49.82827323306886</x:v>
+        <x:v>49.52691347491892</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>-0.06000000000000005</x:v>
+        <x:v>-0.08000000000000007</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.007463479415670658</x:v>
+        <x:v>0.005809018567639265</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6955270047093637</x:v>
+        <x:v>0.697828137500412</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>-0.0969962042578941</x:v>
+        <x:v>-0.12296583350021291</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>48.060075914842116</x:v>
+        <x:v>47.540683329995744</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.32</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.1619787516600275</x:v>
+        <x:v>2.160656498673741</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.45990545274200617</x:v>
+        <x:v>0.46298048451528995</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.34359507459159816</x:v>
+        <x:v>0.36576811980217844</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>56.87190149183196</x:v>
+        <x:v>57.31536239604357</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>51.32249264931842</x:v>
+        <x:v>51.1682676005332</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>46.24742809324514</x:v>
+        <x:v>46.17802682129179</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.919782824415004</x:v>
+        <x:v>0.902297147892582</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.052410788535219605</x:v>
+        <x:v>-0.05174963345459093</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5469762024916136</x:v>
+        <x:v>0.5473635374154877</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.7773965458124836</x:v>
+        <x:v>1.7429856322763857</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>85.54793091624967</x:v>
+        <x:v>84.85971264552771</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.163432003121593</x:v>
+        <x:v>0.18858293392940095</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.02217536301657146</x:v>
+        <x:v>0.022290603716649596</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22637802898667123</x:v>
+        <x:v>0.22634194202141292</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.6239856435596871</x:v>
+        <x:v>0.7346951639966904</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>62.47971287119374</x:v>
+        <x:v>64.6939032799338</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>78.62746550273289</x:v>
+        <x:v>78.80996983584953</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.3200000000000003</x:v>
+        <x:v>0.31000000000000005</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04953488372093022</x:v>
+        <x:v>0.0497078353253652</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5088218259315177</x:v>
+        <x:v>0.5086970336636214</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.5315517190795034</x:v>
+        <x:v>0.5116840623190156</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>60.63103438159007</x:v>
+        <x:v>60.233681246380314</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.44999999999999973</x:v>
+        <x:v>0.3999999999999999</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.03713178294573645</x:v>
+        <x:v>-0.035038860103626945</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.534250006351034</x:v>
+        <x:v>0.5353213985868223</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.91180491746342</x:v>
+        <x:v>0.8126685412764593</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>68.2360983492684</x:v>
+        <x:v>66.25337082552919</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.019999999999999907</x:v>
+        <x:v>0.029999999999999916</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.012622739018087878</x:v>
+        <x:v>-0.012590673575129555</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.1542245797815252</x:v>
+        <x:v>0.15443474040481875</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.2115274949317496</x:v>
+        <x:v>0.27578427925923155</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>54.23054989863499</x:v>
+        <x:v>55.51568558518463</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>15.41</x:v>
+        <x:v>15.21</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.849873754152814</x:v>
+        <x:v>18.844797611147968</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.591218304181021</x:v>
+        <x:v>5.589244498076386</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.615227946220689</x:v>
+        <x:v>-0.6503200231084776</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>37.69544107558622</x:v>
+        <x:v>36.99359953783045</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3619,27 +3619,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E36" s="56" t="n">
-        <x:v>2.8047008127161766</x:v>
+        <x:v>2.8674608290486736</x:v>
       </x:c>
       <x:c r="F36" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G36" s="56" t="n">
-        <x:v>-3.8615249593235617</x:v>
+        <x:v>-3.843107270670175</x:v>
       </x:c>
       <x:c r="H36" s="56" t="n">
-        <x:v>19.585629739935477</x:v>
+        <x:v>19.561548309273117</x:v>
       </x:c>
       <x:c r="I36" s="58" t="n">
         <x:f>IFERROR(C36*(E36-G36)/H36,"")</x:f>
-        <x:v>0.3403631060403013</x:v>
+        <x:v>0.3430489240229372</x:v>
       </x:c>
       <x:c r="J36" s="58" t="n">
         <x:f>IF(I36="","",MAX(0,MIN(100,50+20*I36)))</x:f>
-        <x:v>56.80726212080603</x:v>
+        <x:v>56.86097848045874</x:v>
       </x:c>
       <x:c r="K36" s="54" t="str">
-        <x:v>2026-10-02</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L36" s="54" t="n">
         <x:v>5</x:v>
@@ -3733,7 +3733,7 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>54.63454401541005</x:v>
+        <x:v>54.16995501879927</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>58.49863697160385</x:v>
+        <x:v>58.753822467813286</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>46.24742809324514</x:v>
+        <x:v>46.17802682129179</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>78.62746550273289</x:v>
+        <x:v>78.80996983584953</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>54.63454401541005</x:v>
+        <x:v>54.16995501879927</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>60.24936242351701</x:v>
+        <x:v>60.36913820194163</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>61.64550403377792</x:v>
+        <x:v>61.6278211560705</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>58.47757409274094</x:v>
+        <x:v>58.365188184911354</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.5006203645437454</x:v>
+        <x:v>0.5113509562785417</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.49937963545625463</x:v>
+        <x:v>0.48864904372145834</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>39.43376672454271</x:v>
+        <x:v>39.43805842029876</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>39.39747884308603</x:v>
+        <x:v>39.429098284164795</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>41.01994163653421</x:v>
+        <x:v>41.092885689077264</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>41.163056190467316</x:v>
+        <x:v>41.26265855755927</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>40.72817794569087</x:v>
+        <x:v>40.81583562531746</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>39.69489813856764</x:v>
+        <x:v>39.66673564542544</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>38.32619706160781</x:v>
+        <x:v>38.38522070865495</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>42.60696729044399</x:v>
+        <x:v>42.59663638524673</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>38.108496431809755</x:v>
+        <x:v>38.07732085483303</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>59.32769951131025</x:v>
+        <x:v>59.28608705429261</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.49863697160385</x:v>
+        <x:v>58.753822467813286</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.24742809324514</x:v>
+        <x:v>46.17802682129179</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.62746550273289</x:v>
+        <x:v>78.80996983584953</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.63454401541005</x:v>
+        <x:v>54.16995501879927</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>61.64550403377792</x:v>
+        <x:v>61.6278211560705</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>39.43376672454271</x:v>
+        <x:v>39.43805842029876</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>39.39747884308603</x:v>
+        <x:v>39.429098284164795</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>41.163056190467316</x:v>
+        <x:v>41.26265855755927</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>39.69489813856764</x:v>
+        <x:v>39.66673564542544</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>59.32769951131025</x:v>
+        <x:v>59.28608705429261</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>61.64550403377792</x:v>
+        <x:v>61.6278211560705</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>38.108496431809755</x:v>
+        <x:v>38.07732085483303</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R26678c6ccb234df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1c35a216f42844a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rb5385ff3bb6d4afe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R86aaa2e817154065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rde867f4881d94cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="Rcecdce5dbb1240bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Reca5f147a7d841af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Rc3b69a05020e4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1a70c8b840774903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rd9c44d64a59248db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rfe04e9c96bc84c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R45d3d496d0284b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R775cf2a7ae544213"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R74c232aa274240b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0d4c80a5a954c2d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3c528c5115f46aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R869db1e30fe64c03"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ec2ee917f3d4e70"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-13；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.753822467813286</x:v>
+        <x:v>58.29877809250063</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.17802682129179</x:v>
+        <x:v>46.81147506908014</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.80996983584953</x:v>
+        <x:v>76.67777879995337</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.16995501879927</x:v>
+        <x:v>53.7063730206702</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.6278211560705</x:v>
+        <x:v>60.899978083882196</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.5113509562785417</x:v>
+        <x:v>0.5142187714561656</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.48864904372145834</x:v>
+        <x:v>0.48578122854383443</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.16999999999999993</x:v>
+        <x:v>0.1200000000000001</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.31000000000000005</x:v>
+        <x:v>0.2599999999999998</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.902297147892582</x:v>
+        <x:v>0.851455372155241</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.18858293392940095</x:v>
+        <x:v>0.15838994802753903</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.3999999999999999</x:v>
+        <x:v>0.40000000000000036</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>15.21</x:v>
+        <x:v>15.27</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1666,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.753822467813286</x:v>
+        <x:v>58.29877809250063</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.17802682129179</x:v>
+        <x:v>46.81147506908014</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.80996983584953</x:v>
+        <x:v>76.67777879995337</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,7 +1705,7 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.16995501879927</x:v>
+        <x:v>53.7063730206702</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.6278211560705</x:v>
+        <x:v>60.899978083882196</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>39.43805842029876</x:v>
+        <x:v>40.12544069857022</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>39.429098284164795</x:v>
+        <x:v>40.138435734209224</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>41.092885689077264</x:v>
+        <x:v>41.700416695452056</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>41.26265855755927</x:v>
+        <x:v>41.87050577218652</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>40.81583562531746</x:v>
+        <x:v>41.44516863308049</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>39.66673564542544</x:v>
+        <x:v>40.53243220393831</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>38.38522070865495</x:v>
+        <x:v>39.2756489489682</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>42.59663638524673</x:v>
+        <x:v>43.35544222611075</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>38.07732085483303</x:v>
+        <x:v>38.84666869781766</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>59.28608705429261</x:v>
+        <x:v>58.66704012725816</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1811f571040414f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d8bc89a171425b"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-13。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.9199999999999999</x:v>
+        <x:v>0.9100000000000001</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11533864541832672</x:v>
+        <x:v>-0.11715517241379313</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0932406875238847</x:v>
+        <x:v>1.0971271212424134</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9470363271635067</x:v>
+        <x:v>0.9362225694052826</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>68.94072654327013</x:v>
+        <x:v>68.72445138810565</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.16999999999999993</x:v>
+        <x:v>0.1200000000000001</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.06191235059760948</x:v>
+        <x:v>0.058826259946949525</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0567878027714774</x:v>
+        <x:v>1.063035125394999</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.10227942555631823</x:v>
+        <x:v>0.05754630170881687</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>52.04558851112637</x:v>
+        <x:v>51.15092603417634</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.03590715300805313</x:v>
+        <x:v>0.0358901515151516</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18328083985203292</x:v>
+        <x:v>0.18323908960129281</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.1959132937029416</x:v>
+        <x:v>-0.19586514860581572</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.08173412594117</x:v>
+        <x:v>46.08269702788368</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>58.753822467813286</x:v>
+        <x:v>58.29877809250063</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.33</x:v>
+        <x:v>2.36</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.3432029177718863</x:v>
+        <x:v>2.343214049039102</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5581608045007573</x:v>
+        <x:v>0.5579758747756678</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>-0.023654326254054066</x:v>
+        <x:v>0.030083650063986743</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>49.52691347491892</x:v>
+        <x:v>50.601673001279735</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>-0.08000000000000007</x:v>
+        <x:v>0.009999999999999787</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.005809018567639265</x:v>
+        <x:v>0.005811795891318761</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.697828137500412</x:v>
+        <x:v>0.6975967320952671</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>-0.12296583350021291</x:v>
+        <x:v>0.006003761078555433</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>47.540683329995744</x:v>
+        <x:v>50.120075221571106</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.33</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.160656498673741</x:v>
+        <x:v>2.160775347912526</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.46298048451528995</x:v>
+        <x:v>0.46284997715754084</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.36576811980217844</x:v>
+        <x:v>0.3872197492330672</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>57.31536239604357</x:v>
+        <x:v>57.74439498466134</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>51.1682676005332</x:v>
+        <x:v>52.57593037339619</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>46.17802682129179</x:v>
+        <x:v>46.81147506908014</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.902297147892582</x:v>
+        <x:v>0.851455372155241</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.05174963345459093</x:v>
+        <x:v>-0.05112457808738689</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5473635374154877</x:v>
+        <x:v>0.5476896121579915</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.7429856322763857</x:v>
+        <x:v>1.64797712099433</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>84.85971264552771</x:v>
+        <x:v>82.95954241988659</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.18858293392940095</x:v>
+        <x:v>0.15838994802753903</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.022290603716649596</x:v>
+        <x:v>0.02238479011409658</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22634194202141292</x:v>
+        <x:v>0.2262918803633237</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.7346951639966904</x:v>
+        <x:v>0.6010165176721273</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>64.6939032799338</x:v>
+        <x:v>62.020330353442546</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>78.80996983584953</x:v>
+        <x:v>76.67777879995337</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.31000000000000005</x:v>
+        <x:v>0.2599999999999998</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.0497078353253652</x:v>
+        <x:v>0.04809018567639257</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5086970336636214</x:v>
+        <x:v>0.5129472329510478</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.5116840623190156</x:v>
+        <x:v>0.41312205371391575</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>60.233681246380314</x:v>
+        <x:v>58.262441074278314</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.3999999999999999</x:v>
+        <x:v>0.40000000000000036</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.035038860103626945</x:v>
+        <x:v>-0.03447606727037516</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5353213985868223</x:v>
+        <x:v>0.5352033568373857</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.8126685412764593</x:v>
+        <x:v>0.81179622982519</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>66.25337082552919</x:v>
+        <x:v>66.23592459650379</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3527,21 +3527,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.012590673575129555</x:v>
+        <x:v>-0.01253557567917208</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.15443474040481875</x:v>
+        <x:v>0.15434228779786802</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.27578427925923155</x:v>
+        <x:v>0.275592491766599</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>55.51568558518463</x:v>
+        <x:v>55.51184983533198</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>15.21</x:v>
+        <x:v>15.27</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.844797611147968</x:v>
+        <x:v>18.84242705570291</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.589244498076386</x:v>
+        <x:v>5.5881480490201705</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.6503200231084776</x:v>
+        <x:v>-0.6392864012128852</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>36.99359953783045</x:v>
+        <x:v>37.21427197574229</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3733,7 +3733,7 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>54.16995501879927</x:v>
+        <x:v>53.7063730206702</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>58.753822467813286</x:v>
+        <x:v>58.29877809250063</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>46.17802682129179</x:v>
+        <x:v>46.81147506908014</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>78.80996983584953</x:v>
+        <x:v>76.67777879995337</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>54.16995501879927</x:v>
+        <x:v>53.7063730206702</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>60.36913820194163</x:v>
+        <x:v>59.79192224653928</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>61.6278211560705</x:v>
+        <x:v>60.899978083882196</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>58.365188184911354</x:v>
+        <x:v>57.83983557381913</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.5113509562785417</x:v>
+        <x:v>0.5142187714561656</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.48864904372145834</x:v>
+        <x:v>0.48578122854383443</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>39.43805842029876</x:v>
+        <x:v>40.12544069857022</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>39.429098284164795</x:v>
+        <x:v>40.138435734209224</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>41.092885689077264</x:v>
+        <x:v>41.700416695452056</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>41.26265855755927</x:v>
+        <x:v>41.87050577218652</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>40.81583562531746</x:v>
+        <x:v>41.44516863308049</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>39.66673564542544</x:v>
+        <x:v>40.53243220393831</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>38.38522070865495</x:v>
+        <x:v>39.2756489489682</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>42.59663638524673</x:v>
+        <x:v>43.35544222611075</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>38.07732085483303</x:v>
+        <x:v>38.84666869781766</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>59.28608705429261</x:v>
+        <x:v>58.66704012725816</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.753822467813286</x:v>
+        <x:v>58.29877809250063</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.17802682129179</x:v>
+        <x:v>46.81147506908014</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>78.80996983584953</x:v>
+        <x:v>76.67777879995337</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.16995501879927</x:v>
+        <x:v>53.7063730206702</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>61.6278211560705</x:v>
+        <x:v>60.899978083882196</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>39.43805842029876</x:v>
+        <x:v>40.12544069857022</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>39.429098284164795</x:v>
+        <x:v>40.138435734209224</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>41.26265855755927</x:v>
+        <x:v>41.87050577218652</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>39.66673564542544</x:v>
+        <x:v>40.53243220393831</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>59.28608705429261</x:v>
+        <x:v>58.66704012725816</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>61.6278211560705</x:v>
+        <x:v>60.899978083882196</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>38.07732085483303</x:v>
+        <x:v>38.84666869781766</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Rc3b69a05020e4dca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1a70c8b840774903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rd9c44d64a59248db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rfe04e9c96bc84c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R45d3d496d0284b09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R775cf2a7ae544213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R74c232aa274240b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R56125fca07f24b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R6420639445164efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R30db3398c7124fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Raa4d6d5a9bd74b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rb22c9f4e2f9d4a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R3f02925efa144d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Rb56bee35f03f43ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3c528c5115f46aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ac0622c13f644e0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ec2ee917f3d4e70"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd6f9244081243fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-14；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.29877809250063</x:v>
+        <x:v>58.23840246940734</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.81147506908014</x:v>
+        <x:v>46.14986813431763</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>76.67777879995337</x:v>
+        <x:v>74.09596329714101</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.7063730206702</x:v>
+        <x:v>54.99599293274533</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.899978083882196</x:v>
+        <x:v>60.232623422758266</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.5142187714561656</x:v>
+        <x:v>0.5340617355853953</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.48578122854383443</x:v>
+        <x:v>0.46593826441460473</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.1200000000000001</x:v>
+        <x:v>0.08000000000000007</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.2599999999999998</x:v>
+        <x:v>0.1599999999999997</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.851455372155241</x:v>
+        <x:v>0.808602871528321</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.15838994802753903</x:v>
+        <x:v>0.10335259064235802</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.40000000000000036</x:v>
+        <x:v>0.5499999999999998</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>15.27</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1608,7 +1608,7 @@
       </x:c>
       <x:c r="J16" s="39" t="n">
         <x:f>'因子引擎'!$E$37</x:f>
-        <x:v>-0.494</x:v>
+        <x:v>-0.499</x:v>
       </x:c>
       <x:c r="K16" s="39" t="str">
         <x:v>仍偏宽松</x:v>
@@ -1666,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.29877809250063</x:v>
+        <x:v>58.23840246940734</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.81147506908014</x:v>
+        <x:v>46.14986813431763</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>76.67777879995337</x:v>
+        <x:v>74.09596329714101</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,7 +1705,7 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.7063730206702</x:v>
+        <x:v>54.99599293274533</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.899978083882196</x:v>
+        <x:v>60.232623422758266</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>40.12544069857022</x:v>
+        <x:v>40.73508160764057</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>40.138435734209224</x:v>
+        <x:v>40.64706203611054</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>41.700416695452056</x:v>
+        <x:v>41.81679858867824</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>41.87050577218652</x:v>
+        <x:v>41.93688783077683</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>41.44516863308049</x:v>
+        <x:v>41.677205014876606</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>40.53243220393831</x:v>
+        <x:v>40.59619787952772</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>39.2756489489682</x:v>
+        <x:v>39.3844589704711</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>43.35544222611075</x:v>
+        <x:v>43.049527706579035</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>38.84666869781766</x:v>
+        <x:v>39.78335894775367</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>58.66704012725816</x:v>
+        <x:v>58.438178089607874</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d8bc89a171425b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c400d5e36f14c9c"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-14。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.9100000000000001</x:v>
+        <x:v>0.9400000000000004</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11715517241379313</x:v>
+        <x:v>-0.11645460569913853</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0971271212424134</x:v>
+        <x:v>1.0971008733717773</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9362225694052826</x:v>
+        <x:v>0.9629512028846371</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>68.72445138810565</x:v>
+        <x:v>69.25902405769274</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.1200000000000001</x:v>
+        <x:v>0.08000000000000007</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.058826259946949525</x:v>
+        <x:v>0.05884029158383027</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.063035125394999</x:v>
+        <x:v>1.0626827415045803</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.05754630170881687</x:v>
+        <x:v>0.01991159505066508</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>51.15092603417634</x:v>
+        <x:v>50.398231901013304</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.0358901515151516</x:v>
+        <x:v>0.03587316611452918</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18323908960129281</x:v>
+        <x:v>0.1831973678091879</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.19586514860581572</x:v>
+        <x:v>-0.19581703898657235</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.08269702788368</x:v>
+        <x:v>46.08365922026855</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>58.29877809250063</x:v>
+        <x:v>58.23840246940734</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.36</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.343214049039102</x:v>
+        <x:v>2.343205298013248</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5579758747756678</x:v>
+        <x:v>0.5577910651289777</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>0.030083650063986743</x:v>
+        <x:v>-0.023674273108326926</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>50.601673001279735</x:v>
+        <x:v>49.526514537833464</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>0.009999999999999787</x:v>
+        <x:v>0.010000000000000231</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.005811795891318761</x:v>
+        <x:v>0.0058145695364238475</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6975967320952671</x:v>
+        <x:v>0.697365556745222</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>0.006003761078555433</x:v>
+        <x:v>0.006001773995135099</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>50.120075221571106</x:v>
+        <x:v>50.120035479902704</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.34</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.160775347912526</x:v>
+        <x:v>2.1608741721854314</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.46284997715754084</x:v>
+        <x:v>0.46271252426799164</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.3872197492330672</x:v>
+        <x:v>0.3222861279808338</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>57.74439498466134</x:v>
+        <x:v>56.44572255961668</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>52.57593037339619</x:v>
+        <x:v>51.810009274092664</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -2946,27 +2946,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E19" s="56" t="n">
-        <x:v>198000</x:v>
+        <x:v>198500</x:v>
       </x:c>
       <x:c r="F19" s="57" t="str">
         <x:v>人</x:v>
       </x:c>
       <x:c r="G19" s="56" t="n">
-        <x:v>264694.35215946846</x:v>
+        <x:v>264475.99337748345</x:v>
       </x:c>
       <x:c r="H19" s="56" t="n">
-        <x:v>129535.93781133559</x:v>
+        <x:v>129376.24139969035</x:v>
       </x:c>
       <x:c r="I19" s="58" t="n">
         <x:f>IFERROR(C19*(E19-G19)/H19,"")</x:f>
-        <x:v>0.5148714193632223</x:v>
+        <x:v>0.5099544759045794</x:v>
       </x:c>
       <x:c r="J19" s="58" t="n">
         <x:f>IF(I19="","",MAX(0,MIN(100,50+20*I19)))</x:f>
-        <x:v>60.297428387264446</x:v>
+        <x:v>60.19908951809159</x:v>
       </x:c>
       <x:c r="K19" s="54" t="str">
-        <x:v>2026-10-03</x:v>
+        <x:v>2026-10-10</x:v>
       </x:c>
       <x:c r="L19" s="54" t="n">
         <x:v>5</x:v>
@@ -3011,7 +3011,7 @@
       </x:c>
       <x:c r="J20" s="63" t="n">
         <x:f>SUMPRODUCT(D15:D19,J15:J19)/SUM(D15:D19)</x:f>
-        <x:v>35.53562816112684</x:v>
+        <x:v>35.520877330750906</x:v>
       </x:c>
       <x:c r="K20" s="64" t="str">
         <x:f>IF(J20&gt;=65,"高压",IF(J20&gt;=55,"偏紧",IF(J20&gt;=45,"中性",IF(J20&gt;=35,"偏松","宽松"))))</x:f>
@@ -3102,27 +3102,27 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="E23" s="56" t="n">
-        <x:v>19.641969169567375</x:v>
+        <x:v>16.25598904859684</x:v>
       </x:c>
       <x:c r="F23" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G23" s="56" t="n">
-        <x:v>0.03865234184929262</x:v>
+        <x:v>0.1142404810583327</x:v>
       </x:c>
       <x:c r="H23" s="56" t="n">
-        <x:v>28.69987590646968</x:v>
+        <x:v>28.66433265996694</x:v>
       </x:c>
       <x:c r="I23" s="58" t="n">
         <x:f>IFERROR(C23*(E23-G23)/H23,"")</x:f>
-        <x:v>0.6830453515410148</x:v>
+        <x:v>0.5631301017547263</x:v>
       </x:c>
       <x:c r="J23" s="58" t="n">
         <x:f>IF(I23="","",MAX(0,MIN(100,50+20*I23)))</x:f>
-        <x:v>63.6609070308203</x:v>
+        <x:v>61.26260203509453</x:v>
       </x:c>
       <x:c r="K23" s="54" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L23" s="54" t="n">
         <x:v>5</x:v>
@@ -3167,7 +3167,7 @@
       </x:c>
       <x:c r="J24" s="63" t="n">
         <x:f>SUMPRODUCT(D22:D23,J22:J23)/SUM(D22:D23)</x:f>
-        <x:v>53.57418272328729</x:v>
+        <x:v>52.01528447606554</x:v>
       </x:c>
       <x:c r="K24" s="64" t="str">
         <x:f>IF(J24&gt;=65,"高压",IF(J24&gt;=55,"偏紧",IF(J24&gt;=45,"中性",IF(J24&gt;=35,"偏松","宽松"))))</x:f>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>46.81147506908014</x:v>
+        <x:v>46.14986813431763</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.851455372155241</x:v>
+        <x:v>0.808602871528321</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.05112457808738689</x:v>
+        <x:v>-0.050530022451414754</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5476896121579915</x:v>
+        <x:v>0.547966677439874</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.64797712099433</x:v>
+        <x:v>1.5678560929902616</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>82.95954241988659</x:v>
+        <x:v>81.35712185980523</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.15838994802753903</x:v>
+        <x:v>0.10335259064235802</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.02238479011409658</x:v>
+        <x:v>0.02244078444364586</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.2262918803633237</x:v>
+        <x:v>0.22622358582457355</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.6010165176721273</x:v>
+        <x:v>0.35766299921289246</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>62.020330353442546</x:v>
+        <x:v>57.15325998425785</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>76.67777879995337</x:v>
+        <x:v>74.09596329714101</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.2599999999999998</x:v>
+        <x:v>0.1599999999999997</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04809018567639257</x:v>
+        <x:v>0.04816434724983432</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5129472329510478</x:v>
+        <x:v>0.5127852219471633</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.41312205371391575</x:v>
+        <x:v>0.2180945315184781</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>58.262441074278314</x:v>
+        <x:v>54.36189063036956</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.40000000000000036</x:v>
+        <x:v>0.5499999999999998</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.03447606727037516</x:v>
+        <x:v>-0.033720930232558136</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5352033568373857</x:v>
+        <x:v>0.5352694956892594</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.81179622982519</x:v>
+        <x:v>1.090517832481577</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>66.23592459650379</x:v>
+        <x:v>71.81035664963154</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.029999999999999916</x:v>
+        <x:v>0.05999999999999994</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.01253557567917208</x:v>
+        <x:v>-0.0124418604651163</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.15434228779786802</x:v>
+        <x:v>0.1542644563360042</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.275592491766599</x:v>
+        <x:v>0.46959527933855527</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>55.51184983533198</x:v>
+        <x:v>59.3919055867711</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>15.27</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.84242705570291</x:v>
+        <x:v>18.841119946984747</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.5881480490201705</x:v>
+        <x:v>5.586525661835913</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.6392864012128852</x:v>
+        <x:v>-0.35283467154735537</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>37.21427197574229</x:v>
+        <x:v>42.94330656905289</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3668,27 +3668,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E37" s="56" t="n">
-        <x:v>-0.494</x:v>
+        <x:v>-0.499</x:v>
       </x:c>
       <x:c r="F37" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G37" s="56" t="n">
-        <x:v>-0.43021926910299024</x:v>
+        <x:v>-0.43043377483443734</x:v>
       </x:c>
       <x:c r="H37" s="56" t="n">
-        <x:v>0.15079438018086308</x:v>
+        <x:v>0.1505423216782181</x:v>
       </x:c>
       <x:c r="I37" s="58" t="n">
         <x:f>IFERROR(C37*(E37-G37)/H37,"")</x:f>
-        <x:v>-0.422964906387831</x:v>
+        <x:v>-0.455461456959073</x:v>
       </x:c>
       <x:c r="J37" s="58" t="n">
         <x:f>IF(I37="","",MAX(0,MIN(100,50+20*I37)))</x:f>
-        <x:v>41.54070187224338</x:v>
+        <x:v>40.89077086081854</x:v>
       </x:c>
       <x:c r="K37" s="54" t="str">
-        <x:v>2026-10-02</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="L37" s="54" t="n">
         <x:v>5</x:v>
@@ -3733,7 +3733,7 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>53.7063730206702</x:v>
+        <x:v>54.99599293274533</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>58.29877809250063</x:v>
+        <x:v>58.23840246940734</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>46.81147506908014</x:v>
+        <x:v>46.14986813431763</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>76.67777879995337</x:v>
+        <x:v>74.09596329714101</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>53.7063730206702</x:v>
+        <x:v>54.99599293274533</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>59.79192224653928</x:v>
+        <x:v>58.76468370044604</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>60.899978083882196</x:v>
+        <x:v>60.232623422758266</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>57.83983557381913</x:v>
+        <x:v>57.18753412269295</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.5142187714561656</x:v>
+        <x:v>0.5340617355853953</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.48578122854383443</x:v>
+        <x:v>0.46593826441460473</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>40.12544069857022</x:v>
+        <x:v>40.73508160764057</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>40.138435734209224</x:v>
+        <x:v>40.64706203611054</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>41.700416695452056</x:v>
+        <x:v>41.81679858867824</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>41.87050577218652</x:v>
+        <x:v>41.93688783077683</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>41.44516863308049</x:v>
+        <x:v>41.677205014876606</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>40.53243220393831</x:v>
+        <x:v>40.59619787952772</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>39.2756489489682</x:v>
+        <x:v>39.3844589704711</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>43.35544222611075</x:v>
+        <x:v>43.049527706579035</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>38.84666869781766</x:v>
+        <x:v>39.78335894775367</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>58.66704012725816</x:v>
+        <x:v>58.438178089607874</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.29877809250063</x:v>
+        <x:v>58.23840246940734</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.81147506908014</x:v>
+        <x:v>46.14986813431763</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>76.67777879995337</x:v>
+        <x:v>74.09596329714101</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.7063730206702</x:v>
+        <x:v>54.99599293274533</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>60.899978083882196</x:v>
+        <x:v>60.232623422758266</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>40.12544069857022</x:v>
+        <x:v>40.73508160764057</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>40.138435734209224</x:v>
+        <x:v>40.64706203611054</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>41.87050577218652</x:v>
+        <x:v>41.93688783077683</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>40.53243220393831</x:v>
+        <x:v>40.59619787952772</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>58.66704012725816</x:v>
+        <x:v>58.438178089607874</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>60.899978083882196</x:v>
+        <x:v>60.232623422758266</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>38.84666869781766</x:v>
+        <x:v>39.3844589704711</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R56125fca07f24b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R6420639445164efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R30db3398c7124fda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Raa4d6d5a9bd74b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rb22c9f4e2f9d4a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R3f02925efa144d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Rb56bee35f03f43ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R88c73ebc0e294198"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R8a77f6a2b155477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rf517291a85cb4008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R0edb67aa476d42dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R1ce04768624a4b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R69aa6fc7ff144c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Rddd248ec17ce47cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ac0622c13f644e0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e59285cfcb94b4f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd6f9244081243fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R104b1c157a664ccf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-15；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.23840246940734</x:v>
+        <x:v>56.81961036159685</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.14986813431763</x:v>
+        <x:v>48.45594961581932</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>74.09596329714101</x:v>
+        <x:v>73.93287995925108</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.99599293274533</x:v>
+        <x:v>56.31709751250265</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.232623422758266</x:v>
+        <x:v>60.890684759601235</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1299,7 +1299,7 @@
       <x:c r="I8" s="100"/>
       <x:c r="J8" s="100" t="str">
         <x:f>IF(J6&gt;=65,"高压",IF(J6&gt;=55,"偏紧",IF(J6&gt;=45,"中性",IF(J6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="K8" s="100"/>
       <x:c r="L8" s="100"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.5340617355853953</x:v>
+        <x:v>0.4463977056833203</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.46593826441460473</x:v>
+        <x:v>0.5536022943166796</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.08000000000000007</x:v>
+        <x:v>-0.019999999999999574</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.1599999999999997</x:v>
+        <x:v>0.06000000000000005</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.808602871528321</x:v>
+        <x:v>0.756201876829222</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.10335259064235802</x:v>
+        <x:v>0.14941793137776305</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.5499999999999998</x:v>
+        <x:v>0.6299999999999999</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>16.87</x:v>
+        <x:v>19.99</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1666,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.23840246940734</x:v>
+        <x:v>56.81961036159685</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.14986813431763</x:v>
+        <x:v>48.45594961581932</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>74.09596329714101</x:v>
+        <x:v>73.93287995925108</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,11 +1705,11 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.99599293274533</x:v>
+        <x:v>56.31709751250265</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.232623422758266</x:v>
+        <x:v>60.890684759601235</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>40.73508160764057</x:v>
+        <x:v>40.31743800361548</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>40.64706203611054</x:v>
+        <x:v>40.20210989796185</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>41.81679858867824</x:v>
+        <x:v>41.43644236009874</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>41.93688783077683</x:v>
+        <x:v>41.45505394710223</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>41.677205014876606</x:v>
+        <x:v>41.1123827729922</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>40.59619787952772</x:v>
+        <x:v>41.478335308258536</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>39.3844589704711</x:v>
+        <x:v>39.47631371380632</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>43.049527706579035</x:v>
+        <x:v>44.35901311641114</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>39.78335894775367</x:v>
+        <x:v>39.3145192076643</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>58.438178089607874</x:v>
+        <x:v>58.743274450093146</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c400d5e36f14c9c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aafca0c32a441f9"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-15。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.9400000000000004</x:v>
+        <x:v>0.8600000000000003</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11645460569913853</x:v>
+        <x:v>-0.1151422898742555</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0971008733717773</x:v>
+        <x:v>1.096967024083046</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9629512028846371</x:v>
+        <x:v>0.8889440324693229</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>69.25902405769274</x:v>
+        <x:v>67.77888064938645</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.08000000000000007</x:v>
+        <x:v>-0.019999999999999574</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.05884029158383027</x:v>
+        <x:v>0.058815354070152134</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0626827415045803</x:v>
+        <x:v>1.0619812109323632</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>0.01991159505066508</x:v>
+        <x:v>-0.07421539407552795</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>50.398231901013304</x:v>
+        <x:v>48.51569211848944</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.03587316611452918</x:v>
+        <x:v>0.03583924349881805</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.1831973678091879</x:v>
+        <x:v>0.18311400947195897</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.19581703898657235</x:v>
+        <x:v>-0.19572092600760985</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.08365922026855</x:v>
+        <x:v>46.085581479847804</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>58.23840246940734</x:v>
+        <x:v>56.81961036159685</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.33</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.343205298013248</x:v>
+        <x:v>2.3432473544973575</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5577910651289777</x:v>
+        <x:v>0.557423017622515</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>-0.023674273108326926</x:v>
+        <x:v>0.06593313218280325</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>49.526514537833464</x:v>
+        <x:v>51.31866264365607</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>0.010000000000000231</x:v>
+        <x:v>0.04999999999999982</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.0058145695364238475</x:v>
+        <x:v>0.005879629629629637</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.697365556745222</x:v>
+        <x:v>0.6969061961669237</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>0.006001773995135099</x:v>
+        <x:v>0.06330890816158338</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>50.120035479902704</x:v>
+        <x:v>51.266178163231665</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.31</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.1608741721854314</x:v>
+        <x:v>2.161091269841271</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.46271252426799164</x:v>
+        <x:v>0.46244473038371914</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.3222861279808338</x:v>
+        <x:v>0.34362750771724093</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>56.44572255961668</x:v>
+        <x:v>56.87255015434482</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>51.810009274092664</x:v>
+        <x:v>52.96645932871415</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -3053,27 +3053,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E22" s="56" t="n">
-        <x:v>-0.7829083390764935</x:v>
+        <x:v>3.3810311253439362</x:v>
       </x:c>
       <x:c r="F22" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G22" s="56" t="n">
-        <x:v>1.6825988471851845</x:v>
+        <x:v>1.7052917625095732</x:v>
       </x:c>
       <x:c r="H22" s="56" t="n">
-        <x:v>3.253011654406362</x:v>
+        <x:v>3.23770758860311</x:v>
       </x:c>
       <x:c r="I22" s="58" t="n">
         <x:f>IFERROR(C22*(E22-G22)/H22,"")</x:f>
-        <x:v>-0.757915263820844</x:v>
+        <x:v>0.5175697054091754</x:v>
       </x:c>
       <x:c r="J22" s="58" t="n">
         <x:f>IF(I22="","",MAX(0,MIN(100,50+20*I22)))</x:f>
-        <x:v>34.84169472358312</x:v>
+        <x:v>60.351394108183506</x:v>
       </x:c>
       <x:c r="K22" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L22" s="54" t="n">
         <x:v>5</x:v>
@@ -3167,11 +3167,11 @@
       </x:c>
       <x:c r="J24" s="63" t="n">
         <x:f>SUMPRODUCT(D22:D23,J22:J23)/SUM(D22:D23)</x:f>
-        <x:v>52.01528447606554</x:v>
+        <x:v>60.94367926067568</x:v>
       </x:c>
       <x:c r="K24" s="64" t="str">
         <x:f>IF(J24&gt;=65,"高压",IF(J24&gt;=55,"偏紧",IF(J24&gt;=45,"中性",IF(J24&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="L24" s="64"/>
       <x:c r="M24" s="64"/>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>46.14986813431763</x:v>
+        <x:v>48.45594961581932</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.808602871528321</x:v>
+        <x:v>0.756201876829222</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.050530022451414754</x:v>
+        <x:v>-0.04942179422776924</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.547966677439874</x:v>
+        <x:v>0.5483986376300607</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.5678560929902616</x:v>
+        <x:v>1.4690475427483642</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>81.35712185980523</x:v>
+        <x:v>79.38095085496728</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.10335259064235802</x:v>
+        <x:v>0.14941793137776305</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.02244078444364586</x:v>
+        <x:v>0.022569351232711646</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22622358582457355</x:v>
+        <x:v>0.22609715226077073</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.35766299921289246</x:v>
+        <x:v>0.5610357267956639</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>57.15325998425785</x:v>
+        <x:v>61.22071453591328</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>74.09596329714101</x:v>
+        <x:v>73.93287995925108</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.1599999999999997</x:v>
+        <x:v>0.06000000000000005</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04816434724983432</x:v>
+        <x:v>0.048252812706816674</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5127852219471633</x:v>
+        <x:v>0.5124551910151515</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.2180945315184781</x:v>
+        <x:v>0.022923345297591213</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>54.36189063036956</x:v>
+        <x:v>50.45846690595182</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.5499999999999998</x:v>
+        <x:v>0.6299999999999999</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.033720930232558136</x:v>
+        <x:v>-0.03055699481865281</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5352694956892594</x:v>
+        <x:v>0.5364025586428381</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>1.090517832481577</x:v>
+        <x:v>1.2314575763582112</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>71.81035664963154</x:v>
+        <x:v>74.62915152716423</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.05999999999999994</x:v>
+        <x:v>0.07999999999999996</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.0124418604651163</x:v>
+        <x:v>-0.011994818652849775</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.1542644563360042</x:v>
+        <x:v>0.15447214826789613</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.46959527933855527</x:v>
+        <x:v>0.5955430780525306</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>59.3919055867711</x:v>
+        <x:v>61.91086156105061</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>16.87</x:v>
+        <x:v>19.99</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.841119946984747</x:v>
+        <x:v>18.840304434149562</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.586525661835913</x:v>
+        <x:v>5.583239242326964</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.35283467154735537</x:v>
+        <x:v>0.20591909390779928</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>42.94330656905289</x:v>
+        <x:v>54.118381878155986</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3619,27 +3619,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E36" s="56" t="n">
-        <x:v>2.8674608290486736</x:v>
+        <x:v>1.5826690418555778</x:v>
       </x:c>
       <x:c r="F36" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G36" s="56" t="n">
-        <x:v>-3.843107270670175</x:v>
+        <x:v>-3.8932762266238274</x:v>
       </x:c>
       <x:c r="H36" s="56" t="n">
-        <x:v>19.561548309273117</x:v>
+        <x:v>19.693125027432618</x:v>
       </x:c>
       <x:c r="I36" s="58" t="n">
         <x:f>IFERROR(C36*(E36-G36)/H36,"")</x:f>
-        <x:v>0.3430489240229372</x:v>
+        <x:v>0.2780638045435342</x:v>
       </x:c>
       <x:c r="J36" s="58" t="n">
         <x:f>IF(I36="","",MAX(0,MIN(100,50+20*I36)))</x:f>
-        <x:v>56.86097848045874</x:v>
+        <x:v>55.561276090870685</x:v>
       </x:c>
       <x:c r="K36" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L36" s="54" t="n">
         <x:v>5</x:v>
@@ -3733,11 +3733,11 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>54.99599293274533</x:v>
+        <x:v>56.31709751250265</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="L38" s="64"/>
       <x:c r="M38" s="64"/>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>58.23840246940734</x:v>
+        <x:v>56.81961036159685</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>46.14986813431763</x:v>
+        <x:v>48.45594961581932</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>74.09596329714101</x:v>
+        <x:v>73.93287995925108</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>54.99599293274533</x:v>
+        <x:v>56.31709751250265</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>58.76468370044604</x:v>
+        <x:v>59.02630997987097</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>60.232623422758266</x:v>
+        <x:v>60.890684759601235</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>57.18753412269295</x:v>
+        <x:v>58.45737308785385</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.5340617355853953</x:v>
+        <x:v>0.4463977056833203</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.46593826441460473</x:v>
+        <x:v>0.5536022943166796</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>40.73508160764057</x:v>
+        <x:v>40.31743800361548</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>40.64706203611054</x:v>
+        <x:v>40.20210989796185</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>41.81679858867824</x:v>
+        <x:v>41.43644236009874</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>41.93688783077683</x:v>
+        <x:v>41.45505394710223</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>41.677205014876606</x:v>
+        <x:v>41.1123827729922</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>40.59619787952772</x:v>
+        <x:v>41.478335308258536</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>39.3844589704711</x:v>
+        <x:v>39.47631371380632</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>43.049527706579035</x:v>
+        <x:v>44.35901311641114</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>39.78335894775367</x:v>
+        <x:v>39.3145192076643</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>58.438178089607874</x:v>
+        <x:v>58.743274450093146</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>58.23840246940734</x:v>
+        <x:v>56.81961036159685</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>46.14986813431763</x:v>
+        <x:v>48.45594961581932</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>74.09596329714101</x:v>
+        <x:v>73.93287995925108</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>54.99599293274533</x:v>
+        <x:v>56.31709751250265</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>60.232623422758266</x:v>
+        <x:v>60.890684759601235</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>40.73508160764057</x:v>
+        <x:v>40.31743800361548</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>40.64706203611054</x:v>
+        <x:v>40.20210989796185</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>41.93688783077683</x:v>
+        <x:v>41.45505394710223</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>40.59619787952772</x:v>
+        <x:v>41.478335308258536</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>58.438178089607874</x:v>
+        <x:v>58.743274450093146</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>60.232623422758266</x:v>
+        <x:v>60.890684759601235</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>39.3844589704711</x:v>
+        <x:v>39.3145192076643</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R88c73ebc0e294198"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R8a77f6a2b155477a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rf517291a85cb4008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R0edb67aa476d42dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R1ce04768624a4b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R69aa6fc7ff144c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Rddd248ec17ce47cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R6673cd89eef340a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="Rd83757af55d24571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rc905ebfc2fd94fdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R41258653d9e547b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R4ceb9e17094f46de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="Rad92ca3bd4644b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Ra628941b4f0c4469"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e59285cfcb94b4f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2dfca21ce6694b22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R104b1c157a664ccf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra55e63258cb842bc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-19；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>56.81961036159685</x:v>
+        <x:v>57.287274644304446</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.45594961581932</x:v>
+        <x:v>48.543972455397935</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.93287995925108</x:v>
+        <x:v>75.49397141841702</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.31709751250265</x:v>
+        <x:v>56.89659166645898</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.890684759601235</x:v>
+        <x:v>61.74738562104701</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.4463977056833203</x:v>
+        <x:v>0.4437498599069332</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.5536022943166796</x:v>
+        <x:v>0.5562501400930668</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>-0.019999999999999574</x:v>
+        <x:v>0.009999999999999787</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.06000000000000005</x:v>
+        <x:v>0.17999999999999972</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.756201876829222</x:v>
+        <x:v>0.799555387883543</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.14941793137776305</x:v>
+        <x:v>0.16756527592149095</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>19.99</x:v>
+        <x:v>18.44</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1666,7 +1666,7 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>56.81961036159685</x:v>
+        <x:v>57.287274644304446</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.45594961581932</x:v>
+        <x:v>48.543972455397935</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.93287995925108</x:v>
+        <x:v>75.49397141841702</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,7 +1705,7 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.31709751250265</x:v>
+        <x:v>56.89659166645898</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.890684759601235</x:v>
+        <x:v>61.74738562104701</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>40.31743800361548</x:v>
+        <x:v>39.59858002977813</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>40.20210989796185</x:v>
+        <x:v>39.47290193052207</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>41.43644236009874</x:v>
+        <x:v>40.78111626915918</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>41.45505394710223</x:v>
+        <x:v>40.79558600907938</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>41.1123827729922</x:v>
+        <x:v>40.4306201734108</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>41.478335308258536</x:v>
+        <x:v>40.9448048480407</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>39.47631371380632</x:v>
+        <x:v>38.731051410585444</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>44.35901311641114</x:v>
+        <x:v>44.06985043700938</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>39.3145192076643</x:v>
+        <x:v>38.53583969812086</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>58.743274450093146</x:v>
+        <x:v>59.40466709599137</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aafca0c32a441f9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4221b21991384931"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-19。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.8600000000000003</x:v>
+        <x:v>0.8899999999999997</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.1151422898742555</x:v>
+        <x:v>-0.11447751322751326</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.096967024083046</x:v>
+        <x:v>1.0969085936227185</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.8889440324693229</x:v>
+        <x:v>0.9157349291157098</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>67.77888064938645</x:v>
+        <x:v>68.3146985823142</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>-0.019999999999999574</x:v>
+        <x:v>0.009999999999999787</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.058815354070152134</x:v>
+        <x:v>0.05878306878306871</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0619812109323632</x:v>
+        <x:v>1.0616304783518418</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>-0.07421539407552795</x:v>
+        <x:v>-0.0459510816407641</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>48.51569211848944</x:v>
+        <x:v>49.08097836718472</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.03583924349881805</x:v>
+        <x:v>0.03578847969782822</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18311400947195897</x:v>
+        <x:v>0.18298918460146443</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.19572092600760985</x:v>
+        <x:v>-0.19557702153694284</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.085581479847804</x:v>
+        <x:v>46.08845956926115</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,7 +2503,7 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>56.81961036159685</x:v>
+        <x:v>57.287274644304446</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.38</x:v>
+        <x:v>2.39</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.3432473544973575</x:v>
+        <x:v>2.343278255122277</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.557423017622515</x:v>
+        <x:v>0.5572399504142661</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>0.06593313218280325</x:v>
+        <x:v>0.08384493043434732</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>51.31866264365607</x:v>
+        <x:v>51.67689860868695</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>0.04999999999999982</x:v>
+        <x:v>0.07000000000000028</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.005879629629629637</x:v>
+        <x:v>0.005922009253139466</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6969061961669237</x:v>
+        <x:v>0.6966776499082454</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>0.06330890816158338</x:v>
+        <x:v>0.09197652710015901</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>51.266178163231665</x:v>
+        <x:v>51.83953054200318</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.32</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.161091269841271</x:v>
+        <x:v>2.1611896893588907</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.46244473038371914</x:v>
+        <x:v>0.4623076309211272</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.34362750771724093</x:v>
+        <x:v>0.32188590602454803</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>56.87255015434482</x:v>
+        <x:v>56.43771812049096</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>52.96645932871415</x:v>
+        <x:v>53.16206563888883</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>48.45594961581932</x:v>
+        <x:v>48.543972455397935</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.756201876829222</x:v>
+        <x:v>0.799555387883543</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.04942179422776924</x:v>
+        <x:v>-0.048835888650052665</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5483986376300607</x:v>
+        <x:v>0.5486627307505725</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.4690475427483642</x:v>
+        <x:v>1.5462892392435577</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>79.38095085496728</x:v>
+        <x:v>80.92578478487115</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.14941793137776305</x:v>
+        <x:v>0.16756527592149095</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.022569351232711646</x:v>
+        <x:v>0.02266941743332502</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22609715226077073</x:v>
+        <x:v>0.22605116154977523</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.5610357267956639</x:v>
+        <x:v>0.6409870115012024</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>61.22071453591328</x:v>
+        <x:v>62.81974023002405</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>73.93287995925108</x:v>
+        <x:v>75.49397141841702</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.06000000000000005</x:v>
+        <x:v>0.17999999999999972</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.048252812706816674</x:v>
+        <x:v>0.04833994708994709</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5124551910151515</x:v>
+        <x:v>0.5122967923829889</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.022923345297591213</x:v>
+        <x:v>0.25699956522785455</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>50.45846690595182</x:v>
+        <x:v>55.13999130455709</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3478,21 +3478,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.03055699481865281</x:v>
+        <x:v>-0.02905440414507766</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5364025586428381</x:v>
+        <x:v>0.5366263565856542</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>1.2314575763582112</x:v>
+        <x:v>1.2281439330307695</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>74.62915152716423</x:v>
+        <x:v>74.56287866061538</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.07999999999999996</x:v>
+        <x:v>0.09999999999999998</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.011994818652849775</x:v>
+        <x:v>-0.011696891191709876</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.15447214826789613</x:v>
+        <x:v>0.15446605691865978</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.5955430780525306</x:v>
+        <x:v>0.7231160904853567</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>61.91086156105061</x:v>
+        <x:v>64.46232180970713</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>19.99</x:v>
+        <x:v>18.44</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.840304434149562</x:v>
+        <x:v>18.840039682539672</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.583239242326964</x:v>
+        <x:v>5.581400899511828</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>0.20591909390779928</x:v>
+        <x:v>-0.07167370517582058</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>54.118381878155986</x:v>
+        <x:v>48.56652589648359</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3733,7 +3733,7 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>56.31709751250265</x:v>
+        <x:v>56.89659166645898</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>56.81961036159685</x:v>
+        <x:v>57.287274644304446</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>48.45594961581932</x:v>
+        <x:v>48.543972455397935</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>73.93287995925108</x:v>
+        <x:v>75.49397141841702</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>56.31709751250265</x:v>
+        <x:v>56.89659166645898</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>59.02630997987097</x:v>
+        <x:v>59.689127910420936</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>60.890684759601235</x:v>
+        <x:v>61.74738562104701</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>58.45737308785385</x:v>
+        <x:v>59.134757907621974</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.4463977056833203</x:v>
+        <x:v>0.4437498599069332</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.5536022943166796</x:v>
+        <x:v>0.5562501400930668</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>40.31743800361548</x:v>
+        <x:v>39.59858002977813</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>40.20210989796185</x:v>
+        <x:v>39.47290193052207</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>41.43644236009874</x:v>
+        <x:v>40.78111626915918</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>41.45505394710223</x:v>
+        <x:v>40.79558600907938</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>41.1123827729922</x:v>
+        <x:v>40.4306201734108</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>41.478335308258536</x:v>
+        <x:v>40.9448048480407</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>39.47631371380632</x:v>
+        <x:v>38.731051410585444</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>44.35901311641114</x:v>
+        <x:v>44.06985043700938</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>39.3145192076643</x:v>
+        <x:v>38.53583969812086</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>58.743274450093146</x:v>
+        <x:v>59.40466709599137</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>56.81961036159685</x:v>
+        <x:v>57.287274644304446</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.45594961581932</x:v>
+        <x:v>48.543972455397935</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.93287995925108</x:v>
+        <x:v>75.49397141841702</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.31709751250265</x:v>
+        <x:v>56.89659166645898</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>60.890684759601235</x:v>
+        <x:v>61.74738562104701</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>40.31743800361548</x:v>
+        <x:v>39.59858002977813</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>40.20210989796185</x:v>
+        <x:v>39.47290193052207</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>41.45505394710223</x:v>
+        <x:v>40.79558600907938</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>41.478335308258536</x:v>
+        <x:v>40.9448048480407</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>58.743274450093146</x:v>
+        <x:v>59.40466709599137</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>60.890684759601235</x:v>
+        <x:v>61.74738562104701</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>39.3145192076643</x:v>
+        <x:v>38.53583969812086</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R6673cd89eef340a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="Rd83757af55d24571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rc905ebfc2fd94fdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R41258653d9e547b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R4ceb9e17094f46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="Rad92ca3bd4644b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Ra628941b4f0c4469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R6a81f2cd860c4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1635af7caeec44d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rf4fc6c600d3b4992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R0a39083202e44581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Re2d5bd8a8688433a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R7e065670144c4669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R920952360b934201"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2dfca21ce6694b22"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0e5dd23ae4104fe6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra55e63258cb842bc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bd875f16d7d4a11"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>57.287274644304446</x:v>
+        <x:v>74.83655499836406</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.543972455397935</x:v>
+        <x:v>50.00654275843186</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>75.49397141841702</x:v>
+        <x:v>73.33315387563516</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.89659166645898</x:v>
+        <x:v>53.867597841647815</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.74738562104701</x:v>
+        <x:v>66.9654401660455</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1281,7 +1281,7 @@
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="100" t="str">
         <x:f>IF(A6&gt;=65,"高压",IF(A6&gt;=55,"偏紧",IF(A6&gt;=45,"中性",IF(A6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
       <x:c r="B8" s="100"/>
       <x:c r="C8" s="100"/>
@@ -1299,13 +1299,13 @@
       <x:c r="I8" s="100"/>
       <x:c r="J8" s="100" t="str">
         <x:f>IF(J6&gt;=65,"高压",IF(J6&gt;=55,"偏紧",IF(J6&gt;=45,"中性",IF(J6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="K8" s="100"/>
       <x:c r="L8" s="100"/>
       <x:c r="M8" s="100" t="str">
         <x:f>IF(M6&gt;=65,"高压",IF(M6&gt;=55,"偏紧",IF(M6&gt;=45,"中性",IF(M6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
       <x:c r="N8" s="100"/>
       <x:c r="O8" s="100"/>
@@ -1361,7 +1361,7 @@
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="104" t="str">
         <x:f>'因子引擎'!$B$53</x:f>
-        <x:v>混合状态</x:v>
+        <x:v>政策重定价 + 期限溢价冲击</x:v>
       </x:c>
       <x:c r="B11" s="104"/>
       <x:c r="C11" s="104"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.4437498599069332</x:v>
+        <x:v>0.7526366173917118</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.5562501400930668</x:v>
+        <x:v>0.24736338260828816</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.009999999999999787</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.17999999999999972</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.799555387883543</x:v>
+        <x:v>0.729847215978831</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.16756527592149095</x:v>
+        <x:v>0.15400760358896093</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.6299999999999999</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>18.44</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1608,7 +1608,7 @@
       </x:c>
       <x:c r="J16" s="39" t="n">
         <x:f>'因子引擎'!$E$37</x:f>
-        <x:v>-0.499</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="K16" s="39" t="str">
         <x:v>仍偏宽松</x:v>
@@ -1666,11 +1666,11 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>57.287274644304446</x:v>
+        <x:v>74.83655499836406</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.543972455397935</x:v>
+        <x:v>50.00654275843186</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>75.49397141841702</x:v>
+        <x:v>73.33315387563516</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,11 +1705,11 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.89659166645898</x:v>
+        <x:v>53.867597841647815</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
@@ -1718,11 +1718,11 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>61.74738562104701</x:v>
+        <x:v>66.9654401660455</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1"/>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>39.59858002977813</x:v>
+        <x:v>36.061324041649556</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>39.47290193052207</x:v>
+        <x:v>36.42170776786702</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>40.78111626915918</x:v>
+        <x:v>36.88665337721134</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>40.79558600907938</x:v>
+        <x:v>37.66328142005268</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>40.4306201734108</x:v>
+        <x:v>37.86196498323582</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>40.9448048480407</x:v>
+        <x:v>38.12621889545232</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>38.731051410585444</x:v>
+        <x:v>35.55160686222782</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>44.06985043700938</x:v>
+        <x:v>43.65430684184569</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>38.53583969812086</x:v>
+        <x:v>35.65907255968799</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>59.40466709599137</x:v>
+        <x:v>63.85300652527993</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4221b21991384931"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce0972293f743b4"/>
 </x:worksheet>
 </file>
 
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>0.8899999999999997</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>-0.11447751322751326</x:v>
+        <x:v>0.0017077</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>1.0969085936227185</x:v>
+        <x:v>0.8294249</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>0.9157349291157098</x:v>
+        <x:v>1.2518219551884684</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>68.3146985823142</x:v>
+        <x:v>75.03643910376937</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N5" s="54" t="str">
-        <x:v>2Y与有效联邦基金利率之差，包含2Y期限溢价</x:v>
+        <x:v>可交易的政策路径代理；仍混有2Y期限溢价</x:v>
       </x:c>
       <x:c r="O5" s="54" t="str">
         <x:v>FRED: DGS2-DFF</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.009999999999999787</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.05878306878306871</x:v>
+        <x:v>0.046486</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>1.0616304783518418</x:v>
+        <x:v>0.2391424</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>-0.0459510816407641</x:v>
+        <x:v>1.7709699325590107</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>49.08097836718472</x:v>
+        <x:v>85.41939865118022</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2418,7 +2418,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="54" t="str">
-        <x:v>捕捉政策路径重定价</x:v>
+        <x:v>捕捉政策路径重定价；事件窗口内最有用</x:v>
       </x:c>
       <x:c r="O6" s="54" t="str">
         <x:v>FRED: DGS2</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.03578847969782822</x:v>
+        <x:v>0.0388725</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.18298918460146443</x:v>
+        <x:v>0.1951424</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.19557702153694284</x:v>
+        <x:v>-0.1992006862680791</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.08845956926115</x:v>
+        <x:v>46.015986274638415</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,11 +2503,11 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>57.287274644304446</x:v>
+        <x:v>74.83655499836406</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
       <x:c r="L8" s="64"/>
       <x:c r="M8" s="64"/>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.39</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.343278255122277</x:v>
+        <x:v>2.4457966</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.5572399504142661</x:v>
+        <x:v>0.2887521</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>0.08384493043434732</x:v>
+        <x:v>-0.33176070407799596</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>51.67689860868695</x:v>
+        <x:v>43.36478591844008</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>0.07000000000000028</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>0.005922009253139466</x:v>
+        <x:v>-0.001538</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.6966776499082454</x:v>
+        <x:v>0.1527151</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>0.09197652710015901</x:v>
+        <x:v>0.2719966787829101</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>51.83953054200318</x:v>
+        <x:v>55.4399335756582</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2623,7 +2623,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N11" s="54" t="str">
-        <x:v>适合看边际再定价</x:v>
+        <x:v>适合看边际再定价，不宜单独解释水平</x:v>
       </x:c>
       <x:c r="O11" s="54" t="str">
         <x:v>FRED: T5YIE</x:v>
@@ -2649,21 +2649,21 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.1611896893588907</x:v>
+        <x:v>2.2678783</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.4623076309211272</x:v>
+        <x:v>0.0987903</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.32188590602454803</x:v>
+        <x:v>0.42637485664078395</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>56.43771812049096</x:v>
+        <x:v>58.52749713281568</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N12" s="54" t="str">
-        <x:v>长期通胀锚，含风险与流动性成分</x:v>
+        <x:v>长期锚；同样含风险与流动性成分</x:v>
       </x:c>
       <x:c r="O12" s="54" t="str">
         <x:v>FRED: T5YIFR</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>53.16206563888883</x:v>
+        <x:v>52.139900962779095</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -2750,27 +2750,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E15" s="56" t="n">
-        <x:v>3.0245231607629375</x:v>
+        <x:v>3.0857455</x:v>
       </x:c>
       <x:c r="F15" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G15" s="56" t="n">
-        <x:v>4.286117534594615</x:v>
+        <x:v>4.3677958</x:v>
       </x:c>
       <x:c r="H15" s="56" t="n">
-        <x:v>0.8540343631541617</x:v>
+        <x:v>0.6830206</x:v>
       </x:c>
       <x:c r="I15" s="58" t="n">
         <x:f>IFERROR(C15*(E15-G15)/H15,"")</x:f>
-        <x:v>-1.4772173442439656</x:v>
+        <x:v>-1.8770302096305733</x:v>
       </x:c>
       <x:c r="J15" s="58" t="n">
         <x:f>IF(I15="","",MAX(0,MIN(100,50+20*I15)))</x:f>
-        <x:v>20.45565311512069</x:v>
+        <x:v>12.459395807388532</x:v>
       </x:c>
       <x:c r="K15" s="54" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="L15" s="54" t="n">
         <x:v>5</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N15" s="54" t="str">
-        <x:v>平均时薪同比；CES会月度及年度修订</x:v>
+        <x:v>月频、构成效应明显；CES会月度及年度修订</x:v>
       </x:c>
       <x:c r="O15" s="54" t="str">
         <x:v>BLS/FRED: CES0500000003</x:v>
@@ -2848,27 +2848,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E17" s="56" t="n">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="F17" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G17" s="56" t="n">
-        <x:v>4.128985507246377</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="H17" s="56" t="n">
-        <x:v>0.862469342895114</x:v>
+        <x:v>0.3550125</x:v>
       </x:c>
       <x:c r="I17" s="58" t="n">
         <x:f>IFERROR(C17*(E17-G17)/H17,"")</x:f>
-        <x:v>-0.08233857045311783</x:v>
+        <x:v>-0.33801626703285</x:v>
       </x:c>
       <x:c r="J17" s="58" t="n">
         <x:f>IF(I17="","",MAX(0,MIN(100,50+20*I17)))</x:f>
-        <x:v>48.35322859093765</x:v>
+        <x:v>43.239674659343</x:v>
       </x:c>
       <x:c r="K17" s="54" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="L17" s="54" t="n">
         <x:v>5</x:v>
@@ -2877,7 +2877,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N17" s="54" t="str">
-        <x:v>家庭调查月频；单月变化需谨慎</x:v>
+        <x:v>家庭调查月频；样本波动大，单月变化需谨慎</x:v>
       </x:c>
       <x:c r="O17" s="54" t="str">
         <x:v>BLS/FRED: UNRATE</x:v>
@@ -2897,27 +2897,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E18" s="56" t="n">
-        <x:v>7079</x:v>
+        <x:v>7271</x:v>
       </x:c>
       <x:c r="F18" s="57" t="str">
         <x:v>千人</x:v>
       </x:c>
       <x:c r="G18" s="56" t="n">
-        <x:v>8822.54411764706</x:v>
+        <x:v>8847.2623</x:v>
       </x:c>
       <x:c r="H18" s="56" t="n">
-        <x:v>1702.9875367316663</x:v>
+        <x:v>1750.1508</x:v>
       </x:c>
       <x:c r="I18" s="58" t="n">
         <x:f>IFERROR(C18*(E18-G18)/H18,"")</x:f>
-        <x:v>-1.0238149604977311</x:v>
+        <x:v>-0.9006437045310612</x:v>
       </x:c>
       <x:c r="J18" s="58" t="n">
         <x:f>IF(I18="","",MAX(0,MIN(100,50+20*I18)))</x:f>
-        <x:v>29.52370079004538</x:v>
+        <x:v>31.987125909378776</x:v>
       </x:c>
       <x:c r="K18" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="L18" s="54" t="n">
         <x:v>5</x:v>
@@ -2926,7 +2926,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N18" s="54" t="str">
-        <x:v>约1个月滞后，月度与年度修订较大</x:v>
+        <x:v>并非高频；约1个月滞后、月度与年度修订较大</x:v>
       </x:c>
       <x:c r="O18" s="54" t="str">
         <x:v>BLS/FRED: JTSJOL</x:v>
@@ -2946,27 +2946,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E19" s="56" t="n">
-        <x:v>198500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="F19" s="57" t="str">
         <x:v>人</x:v>
       </x:c>
       <x:c r="G19" s="56" t="n">
-        <x:v>264475.99337748345</x:v>
+        <x:v>223663.7931</x:v>
       </x:c>
       <x:c r="H19" s="56" t="n">
-        <x:v>129376.24139969035</x:v>
+        <x:v>22445.2484</x:v>
       </x:c>
       <x:c r="I19" s="58" t="n">
         <x:f>IFERROR(C19*(E19-G19)/H19,"")</x:f>
-        <x:v>0.5099544759045794</x:v>
+        <x:v>0.7869724934743877</x:v>
       </x:c>
       <x:c r="J19" s="58" t="n">
         <x:f>IF(I19="","",MAX(0,MIN(100,50+20*I19)))</x:f>
-        <x:v>60.19908951809159</x:v>
+        <x:v>65.73944986948776</x:v>
       </x:c>
       <x:c r="K19" s="54" t="str">
-        <x:v>2026-10-10</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="L19" s="54" t="n">
         <x:v>5</x:v>
@@ -2975,7 +2975,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N19" s="54" t="str">
-        <x:v>周频四周均值；受季调、假期与州级申报扰动</x:v>
+        <x:v>周频且及时；受季调、假期与州级申报扰动</x:v>
       </x:c>
       <x:c r="O19" s="54" t="str">
         <x:v>DOL/FRED: ICSA</x:v>
@@ -3011,11 +3011,11 @@
       </x:c>
       <x:c r="J20" s="63" t="n">
         <x:f>SUMPRODUCT(D15:D19,J15:J19)/SUM(D15:D19)</x:f>
-        <x:v>35.520877330750906</x:v>
+        <x:v>34.07851899065477</x:v>
       </x:c>
       <x:c r="K20" s="64" t="str">
         <x:f>IF(J20&gt;=65,"高压",IF(J20&gt;=55,"偏紧",IF(J20&gt;=45,"中性",IF(J20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏松</x:v>
+        <x:v>宽松</x:v>
       </x:c>
       <x:c r="L20" s="64"/>
       <x:c r="M20" s="64"/>
@@ -3053,27 +3053,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E22" s="56" t="n">
-        <x:v>3.3810311253439362</x:v>
+        <x:v>-0.7829083</x:v>
       </x:c>
       <x:c r="F22" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G22" s="56" t="n">
-        <x:v>1.7052917625095732</x:v>
+        <x:v>1.1590888</x:v>
       </x:c>
       <x:c r="H22" s="56" t="n">
-        <x:v>3.23770758860311</x:v>
+        <x:v>3.0031765</x:v>
       </x:c>
       <x:c r="I22" s="58" t="n">
         <x:f>IFERROR(C22*(E22-G22)/H22,"")</x:f>
-        <x:v>0.5175697054091754</x:v>
+        <x:v>-0.6466476745539265</x:v>
       </x:c>
       <x:c r="J22" s="58" t="n">
         <x:f>IF(I22="","",MAX(0,MIN(100,50+20*I22)))</x:f>
-        <x:v>60.351394108183506</x:v>
+        <x:v>37.06704650892147</x:v>
       </x:c>
       <x:c r="K22" s="54" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="L22" s="54" t="n">
         <x:v>5</x:v>
@@ -3082,7 +3082,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N22" s="54" t="str">
-        <x:v>广谱上游价格三个月变化，不等于最终消费价格</x:v>
+        <x:v>广谱上游价格月频代理；不等于最终消费价格</x:v>
       </x:c>
       <x:c r="O22" s="54" t="str">
         <x:v>BLS/FRED: PPIACO</x:v>
@@ -3102,27 +3102,27 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="E23" s="56" t="n">
-        <x:v>16.25598904859684</x:v>
+        <x:v>43.4199946</x:v>
       </x:c>
       <x:c r="F23" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G23" s="56" t="n">
-        <x:v>0.1142404810583327</x:v>
+        <x:v>2.3565562</x:v>
       </x:c>
       <x:c r="H23" s="56" t="n">
-        <x:v>28.66433265996694</x:v>
+        <x:v>19.3365269</x:v>
       </x:c>
       <x:c r="I23" s="58" t="n">
         <x:f>IFERROR(C23*(E23-G23)/H23,"")</x:f>
-        <x:v>0.5631301017547263</x:v>
+        <x:v>2.123620162625999</x:v>
       </x:c>
       <x:c r="J23" s="58" t="n">
         <x:f>IF(I23="","",MAX(0,MIN(100,50+20*I23)))</x:f>
-        <x:v>61.26260203509453</x:v>
+        <x:v>92.47240325251998</x:v>
       </x:c>
       <x:c r="K23" s="54" t="str">
-        <x:v>2026-10-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L23" s="54" t="n">
         <x:v>5</x:v>
@@ -3131,7 +3131,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N23" s="54" t="str">
-        <x:v>高频能源价格变化，不能代表核心服务通胀</x:v>
+        <x:v>高频且准确反映能源；不能代表核心服务通胀</x:v>
       </x:c>
       <x:c r="O23" s="54" t="str">
         <x:v>EIA/FRED: DCOILWTICO</x:v>
@@ -3167,11 +3167,11 @@
       </x:c>
       <x:c r="J24" s="63" t="n">
         <x:f>SUMPRODUCT(D22:D23,J22:J23)/SUM(D22:D23)</x:f>
-        <x:v>60.94367926067568</x:v>
+        <x:v>73.0805283922605</x:v>
       </x:c>
       <x:c r="K24" s="64" t="str">
         <x:f>IF(J24&gt;=65,"高压",IF(J24&gt;=55,"偏紧",IF(J24&gt;=45,"中性",IF(J24&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>高压</x:v>
       </x:c>
       <x:c r="L24" s="64"/>
       <x:c r="M24" s="64"/>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>48.543972455397935</x:v>
+        <x:v>50.00654275843186</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.799555387883543</x:v>
+        <x:v>0.729847215978831</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.048835888650052665</x:v>
+        <x:v>-0.048298865819274124</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5486627307505725</x:v>
+        <x:v>0.5488544542960424</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.5462892392435577</x:v>
+        <x:v>1.4177639913593318</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>80.92578478487115</x:v>
+        <x:v>78.35527982718664</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.16756527592149095</x:v>
+        <x:v>0.15400760358896093</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.02266941743332502</x:v>
+        <x:v>0.022759995492742695</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22605116154977523</x:v>
+        <x:v>0.22599946658696593</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.6409870115012024</x:v>
+        <x:v>0.5807429994340867</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>62.81974023002405</x:v>
+        <x:v>61.61485998868173</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>75.49397141841702</x:v>
+        <x:v>73.33315387563516</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.17999999999999972</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.04833994708994709</x:v>
+        <x:v>0.038659</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.5122967923829889</x:v>
+        <x:v>0.1966126</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>0.25699956522785455</x:v>
+        <x:v>1.2274950842418035</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>55.13999130455709</x:v>
+        <x:v>74.54990168483607</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.6299999999999999</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.02905440414507766</x:v>
+        <x:v>-0.025786</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.5366263565856542</x:v>
+        <x:v>0.2641338</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>1.2281439330307695</x:v>
+        <x:v>0.5897995637059703</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>74.56287866061538</x:v>
+        <x:v>61.7959912741194</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.09999999999999998</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.011696891191709876</x:v>
+        <x:v>-0.0080372</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.15446605691865978</x:v>
+        <x:v>0.0636386</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.7231160904853567</x:v>
+        <x:v>0.2834317536840848</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>64.46232180970713</x:v>
+        <x:v>55.6686350736817</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3550,7 +3550,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N34" s="54" t="str">
-        <x:v>投资级信用条件确认指标</x:v>
+        <x:v>比高收益更稳健，但对早期风险反应较弱</x:v>
       </x:c>
       <x:c r="O34" s="54" t="str">
         <x:v>FRED: BAMLC0A0CM</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>18.44</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>18.840039682539672</x:v>
+        <x:v>19.129697</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.581400899511828</x:v>
+        <x:v>5.2749403</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.07167370517582058</x:v>
+        <x:v>-0.36582347671309207</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>48.56652589648359</x:v>
+        <x:v>42.68353046573816</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-10-19</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3619,27 +3619,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E36" s="56" t="n">
-        <x:v>1.5826690418555778</x:v>
+        <x:v>-0.1231008</x:v>
       </x:c>
       <x:c r="F36" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G36" s="56" t="n">
-        <x:v>-3.8932762266238274</x:v>
+        <x:v>0.0573589</x:v>
       </x:c>
       <x:c r="H36" s="56" t="n">
-        <x:v>19.693125027432618</x:v>
+        <x:v>1.1875496</x:v>
       </x:c>
       <x:c r="I36" s="58" t="n">
         <x:f>IFERROR(C36*(E36-G36)/H36,"")</x:f>
-        <x:v>0.2780638045435342</x:v>
+        <x:v>-0.1519597160404921</x:v>
       </x:c>
       <x:c r="J36" s="58" t="n">
         <x:f>IF(I36="","",MAX(0,MIN(100,50+20*I36)))</x:f>
-        <x:v>55.561276090870685</x:v>
+        <x:v>46.96080567919016</x:v>
       </x:c>
       <x:c r="K36" s="54" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L36" s="54" t="n">
         <x:v>5</x:v>
@@ -3668,27 +3668,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E37" s="56" t="n">
-        <x:v>-0.499</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="F37" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G37" s="56" t="n">
-        <x:v>-0.43043377483443734</x:v>
+        <x:v>-0.3977854</x:v>
       </x:c>
       <x:c r="H37" s="56" t="n">
-        <x:v>0.1505423216782181</x:v>
+        <x:v>0.1335983</x:v>
       </x:c>
       <x:c r="I37" s="58" t="n">
         <x:f>IFERROR(C37*(E37-G37)/H37,"")</x:f>
-        <x:v>-0.455461456959073</x:v>
+        <x:v>-1.2141965878308334</x:v>
       </x:c>
       <x:c r="J37" s="58" t="n">
         <x:f>IF(I37="","",MAX(0,MIN(100,50+20*I37)))</x:f>
-        <x:v>40.89077086081854</x:v>
+        <x:v>25.716068243383333</x:v>
       </x:c>
       <x:c r="K37" s="54" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L37" s="54" t="n">
         <x:v>5</x:v>
@@ -3697,7 +3697,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N37" s="54" t="str">
-        <x:v>周频综合金融条件；负值代表相对宽松</x:v>
+        <x:v>周频综合金融条件；负值代表较历史均值宽松</x:v>
       </x:c>
       <x:c r="O37" s="54" t="str">
         <x:v>Chicago Fed/FRED: NFCI</x:v>
@@ -3733,11 +3733,11 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>56.89659166645898</x:v>
+        <x:v>53.867597841647815</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏紧</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="L38" s="64"/>
       <x:c r="M38" s="64"/>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>57.287274644304446</x:v>
+        <x:v>74.83655499836406</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>48.543972455397935</x:v>
+        <x:v>50.00654275843186</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>75.49397141841702</x:v>
+        <x:v>73.33315387563516</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>56.89659166645898</x:v>
+        <x:v>53.867597841647815</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>59.689127910420936</x:v>
+        <x:v>65.69503037756913</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>61.74738562104701</x:v>
+        <x:v>66.9654401660455</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>59.134757907621974</x:v>
+        <x:v>58.16284261855763</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.4437498599069332</x:v>
+        <x:v>0.7526366173917118</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.5562501400930668</x:v>
+        <x:v>0.24736338260828816</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4127,7 +4127,7 @@
       </x:c>
       <x:c r="B53" s="68" t="str">
         <x:f>IF(AND(B42&gt;=60,B44&gt;=60,B43&lt;60),"政策重定价 + 期限溢价冲击",IF(AND(B46&gt;=65,B45&gt;=60),"全面收紧传导",IF(AND(B43&gt;=60,B44&gt;=60),"通胀与期限溢价共振",IF(AND(B42&gt;=60,B43&lt;55,B45&lt;55),"政策独涨/预防性加息",IF(AND(B46&lt;=40,B45&lt;=45),"宽松传导","混合状态")))))</x:f>
-        <x:v>混合状态</x:v>
+        <x:v>政策重定价 + 期限溢价冲击</x:v>
       </x:c>
       <x:c r="C53" s="68" t="str">
         <x:v>规则优先于主观叙事</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>39.59858002977813</x:v>
+        <x:v>36.061324041649556</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>39.47290193052207</x:v>
+        <x:v>36.42170776786702</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>40.78111626915918</x:v>
+        <x:v>36.88665337721134</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>40.79558600907938</x:v>
+        <x:v>37.66328142005268</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>40.4306201734108</x:v>
+        <x:v>37.86196498323582</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>40.9448048480407</x:v>
+        <x:v>38.12621889545232</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>38.731051410585444</x:v>
+        <x:v>35.55160686222782</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,7 +4572,7 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>44.06985043700938</x:v>
+        <x:v>43.65430684184569</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>38.53583969812086</x:v>
+        <x:v>35.65907255968799</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>59.40466709599137</x:v>
+        <x:v>63.85300652527993</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>57.287274644304446</x:v>
+        <x:v>74.83655499836406</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>48.543972455397935</x:v>
+        <x:v>50.00654275843186</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>75.49397141841702</x:v>
+        <x:v>73.33315387563516</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>56.89659166645898</x:v>
+        <x:v>53.867597841647815</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>61.74738562104701</x:v>
+        <x:v>66.9654401660455</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>39.59858002977813</x:v>
+        <x:v>36.061324041649556</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>39.47290193052207</x:v>
+        <x:v>36.42170776786702</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>40.79558600907938</x:v>
+        <x:v>37.66328142005268</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>40.9448048480407</x:v>
+        <x:v>38.12621889545232</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>59.40466709599137</x:v>
+        <x:v>63.85300652527993</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>61.74738562104701</x:v>
+        <x:v>66.9654401660455</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>38.53583969812086</x:v>
+        <x:v>35.55160686222782</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R6a81f2cd860c4776"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R1635af7caeec44d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rf4fc6c600d3b4992"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R0a39083202e44581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Re2d5bd8a8688433a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R7e065670144c4669"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R920952360b934201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Re4f4d76ef8b348b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R70c0be9ed9e645af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R2f00e376ec89412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R78832e063adc47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rc435d777cd4c42b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R2484796737584f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R6f6c6938cf014b64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0e5dd23ae4104fe6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbaa0d9f96026448d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bd875f16d7d4a11"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R640023285cbc4aff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1136,49 +1136,49 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="N3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
       <x:c r="O3" s="10" t="str">
-        <x:v>当前快照截至 2026-10-20；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
+        <x:v>当前快照截至 2026-10-22；官方数据经 FRED、纽约联储、BLS、DOL、EIA、Atlanta Fed 交叉核验。高分=利率/金融条件压力更大。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1"/>
@@ -1232,31 +1232,31 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="99" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>74.83655499836406</x:v>
+        <x:v>57.22829360240057</x:v>
       </x:c>
       <x:c r="B6" s="99"/>
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>50.00654275843186</x:v>
+        <x:v>49.95917150829179</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
       <x:c r="G6" s="99" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.33315387563516</x:v>
+        <x:v>72.8049594006678</x:v>
       </x:c>
       <x:c r="H6" s="99"/>
       <x:c r="I6" s="99"/>
       <x:c r="J6" s="99" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.867597841647815</x:v>
+        <x:v>53.73195428302721</x:v>
       </x:c>
       <x:c r="K6" s="99"/>
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>66.9654401660455</x:v>
+        <x:v>60.46469053817076</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1281,7 +1281,7 @@
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="100" t="str">
         <x:f>IF(A6&gt;=65,"高压",IF(A6&gt;=55,"偏紧",IF(A6&gt;=45,"中性",IF(A6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="B8" s="100"/>
       <x:c r="C8" s="100"/>
@@ -1305,7 +1305,7 @@
       <x:c r="L8" s="100"/>
       <x:c r="M8" s="100" t="str">
         <x:f>IF(M6&gt;=65,"高压",IF(M6&gt;=55,"偏紧",IF(M6&gt;=45,"中性",IF(M6&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="N8" s="100"/>
       <x:c r="O8" s="100"/>
@@ -1361,7 +1361,7 @@
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="104" t="str">
         <x:f>'因子引擎'!$B$53</x:f>
-        <x:v>政策重定价 + 期限溢价冲击</x:v>
+        <x:v>混合状态</x:v>
       </x:c>
       <x:c r="B11" s="104"/>
       <x:c r="C11" s="104"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.7526366173917118</x:v>
+        <x:v>0.47639071404866157</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.24736338260828816</x:v>
+        <x:v>0.5236092859513384</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1467,7 +1467,7 @@
       </x:c>
       <x:c r="J13" s="111" t="n">
         <x:f>'因子引擎'!$E$6</x:f>
-        <x:v>0.47</x:v>
+        <x:v>-0.040000000000000036</x:v>
       </x:c>
       <x:c r="K13" s="39" t="str">
         <x:v>+47bp</x:v>
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="M13" s="111" t="n">
         <x:f>'因子引擎'!$E$32</x:f>
-        <x:v>0.28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="39" t="str">
         <x:v>+28bp</x:v>
@@ -1514,7 +1514,7 @@
       </x:c>
       <x:c r="J14" s="111" t="n">
         <x:f>'因子引擎'!$E$28</x:f>
-        <x:v>0.729847215978831</x:v>
+        <x:v>0.718008053968759</x:v>
       </x:c>
       <x:c r="K14" s="39" t="str">
         <x:v>高于5年中枢</x:v>
@@ -1524,7 +1524,7 @@
       </x:c>
       <x:c r="M14" s="111" t="n">
         <x:f>'因子引擎'!$E$29</x:f>
-        <x:v>0.15400760358896093</x:v>
+        <x:v>0.14629031404763104</x:v>
       </x:c>
       <x:c r="N14" s="39" t="str">
         <x:v>边际回落</x:v>
@@ -1561,7 +1561,7 @@
       </x:c>
       <x:c r="J15" s="111" t="n">
         <x:f>'因子引擎'!$E$33</x:f>
-        <x:v>0.13</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="K15" s="39" t="str">
         <x:v>+13bp</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="M15" s="111" t="n">
         <x:f>'因子引擎'!$E$35</x:f>
-        <x:v>17.2</x:v>
+        <x:v>16.68</x:v>
       </x:c>
       <x:c r="N15" s="39" t="str">
         <x:v>低于5年均值</x:v>
@@ -1608,7 +1608,7 @@
       </x:c>
       <x:c r="J16" s="39" t="n">
         <x:f>'因子引擎'!$E$37</x:f>
-        <x:v>-0.56</x:v>
+        <x:v>-0.496</x:v>
       </x:c>
       <x:c r="K16" s="39" t="str">
         <x:v>仍偏宽松</x:v>
@@ -1666,11 +1666,11 @@
       </x:c>
       <x:c r="B20" s="43" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>74.83655499836406</x:v>
+        <x:v>57.22829360240057</x:v>
       </x:c>
       <x:c r="C20" s="39" t="str">
         <x:f>IF(B20&gt;=65,"高压",IF(B20&gt;=55,"偏紧",IF(B20&gt;=45,"中性",IF(B20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>50.00654275843186</x:v>
+        <x:v>49.95917150829179</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1692,7 +1692,7 @@
       </x:c>
       <x:c r="B22" s="43" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.33315387563516</x:v>
+        <x:v>72.8049594006678</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:f>IF(B22&gt;=65,"高压",IF(B22&gt;=55,"偏紧",IF(B22&gt;=45,"中性",IF(B22&gt;=35,"偏松","宽松"))))</x:f>
@@ -1705,7 +1705,7 @@
       </x:c>
       <x:c r="B23" s="43" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.867597841647815</x:v>
+        <x:v>53.73195428302721</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:f>IF(B23&gt;=65,"高压",IF(B23&gt;=55,"偏紧",IF(B23&gt;=45,"中性",IF(B23&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,11 +1718,11 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>66.9654401660455</x:v>
+        <x:v>60.46469053817076</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1"/>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>36.061324041649556</x:v>
+        <x:v>40.78190734974757</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>36.42170776786702</x:v>
+        <x:v>40.8430394023309</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>36.88665337721134</x:v>
+        <x:v>42.258986122741376</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>37.66328142005268</x:v>
+        <x:v>42.38848017160706</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>37.86196498323582</x:v>
+        <x:v>41.951299318883656</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>38.12621889545232</x:v>
+        <x:v>42.65079341806066</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>35.55160686222782</x:v>
+        <x:v>40.764492188550186</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,11 +1858,11 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>43.65430684184569</x:v>
+        <x:v>45.78407918986468</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
-        <x:v>偏不利</x:v>
+        <x:v>中性</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>35.65907255968799</x:v>
+        <x:v>39.619700514709706</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>63.85300652527993</x:v>
+        <x:v>58.06173864479713</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce0972293f743b4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27057fb4ed8f4b02"/>
 </x:worksheet>
 </file>
 
@@ -2234,49 +2234,49 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="C3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="D3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="E3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="F3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="G3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="H3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="I3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="J3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="K3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="L3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="M3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="N3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
       <x:c r="O3" s="53" t="str">
-        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-20。 </x:v>
+        <x:v>名义利率 = 预期政策路径 + 通胀补偿 + 期限溢价；风险资产压力再经过市场传导门控。蓝色单元格为可更新输入。 数据截至 2026-10-22。 </x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -2340,27 +2340,27 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>1.04</x:v>
+        <x:v>0.9299999999999997</x:v>
       </x:c>
       <x:c r="F5" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G5" s="56" t="n">
-        <x:v>0.0017077</x:v>
+        <x:v>-0.11311096433289304</x:v>
       </x:c>
       <x:c r="H5" s="56" t="n">
-        <x:v>0.8294249</x:v>
+        <x:v>1.0968276213864914</x:v>
       </x:c>
       <x:c r="I5" s="58" t="n">
         <x:f>IFERROR(C5*(E5-G5)/H5,"")</x:f>
-        <x:v>1.2518219551884684</x:v>
+        <x:v>0.9510254337088122</x:v>
       </x:c>
       <x:c r="J5" s="58" t="n">
         <x:f>IF(I5="","",MAX(0,MIN(100,50+20*I5)))</x:f>
-        <x:v>75.03643910376937</x:v>
+        <x:v>69.02050867417624</x:v>
       </x:c>
       <x:c r="K5" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L5" s="54" t="n">
         <x:v>5</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N5" s="54" t="str">
-        <x:v>可交易的政策路径代理；仍混有2Y期限溢价</x:v>
+        <x:v>2Y与有效联邦基金利率之差，包含2Y期限溢价</x:v>
       </x:c>
       <x:c r="O5" s="54" t="str">
         <x:v>FRED: DGS2-DFF</x:v>
@@ -2389,27 +2389,27 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E6" s="56" t="n">
-        <x:v>0.47</x:v>
+        <x:v>-0.040000000000000036</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G6" s="56" t="n">
-        <x:v>0.046486</x:v>
+        <x:v>0.0587318361955085</x:v>
       </x:c>
       <x:c r="H6" s="56" t="n">
-        <x:v>0.2391424</x:v>
+        <x:v>1.060931752358709</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>IFERROR(C6*(E6-G6)/H6,"")</x:f>
-        <x:v>1.7709699325590107</x:v>
+        <x:v>-0.0930614396034464</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>IF(I6="","",MAX(0,MIN(100,50+20*I6)))</x:f>
-        <x:v>85.41939865118022</x:v>
+        <x:v>48.13877120793107</x:v>
       </x:c>
       <x:c r="K6" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L6" s="54" t="n">
         <x:v>5</x:v>
@@ -2418,7 +2418,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="54" t="str">
-        <x:v>捕捉政策路径重定价；事件窗口内最有用</x:v>
+        <x:v>捕捉政策路径重定价</x:v>
       </x:c>
       <x:c r="O6" s="54" t="str">
         <x:v>FRED: DGS2</x:v>
@@ -2444,21 +2444,21 @@
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G7" s="56" t="n">
-        <x:v>0.0388725</x:v>
+        <x:v>0.035754716981132154</x:v>
       </x:c>
       <x:c r="H7" s="56" t="n">
-        <x:v>0.1951424</x:v>
+        <x:v>0.18290610940425073</x:v>
       </x:c>
       <x:c r="I7" s="58" t="n">
         <x:f>IFERROR(C7*(E7-G7)/H7,"")</x:f>
-        <x:v>-0.1992006862680791</x:v>
+        <x:v>-0.1954812613837229</x:v>
       </x:c>
       <x:c r="J7" s="58" t="n">
         <x:f>IF(I7="","",MAX(0,MIN(100,50+20*I7)))</x:f>
-        <x:v>46.015986274638415</x:v>
+        <x:v>46.09037477232554</x:v>
       </x:c>
       <x:c r="K7" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L7" s="54" t="n">
         <x:v>5</x:v>
@@ -2503,11 +2503,11 @@
       </x:c>
       <x:c r="J8" s="63" t="n">
         <x:f>SUMPRODUCT(D5:D7,J5:J7)/SUM(D5:D7)</x:f>
-        <x:v>74.83655499836406</x:v>
+        <x:v>57.22829360240057</x:v>
       </x:c>
       <x:c r="K8" s="64" t="str">
         <x:f>IF(J8&gt;=65,"高压",IF(J8&gt;=55,"偏紧",IF(J8&gt;=45,"中性",IF(J8&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>高压</x:v>
+        <x:v>偏紧</x:v>
       </x:c>
       <x:c r="L8" s="64"/>
       <x:c r="M8" s="64"/>
@@ -2545,27 +2545,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E10" s="56" t="n">
-        <x:v>2.35</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G10" s="56" t="n">
-        <x:v>2.4457966</x:v>
+        <x:v>2.3433861386138646</x:v>
       </x:c>
       <x:c r="H10" s="56" t="n">
-        <x:v>0.2887521</x:v>
+        <x:v>0.556880422733508</x:v>
       </x:c>
       <x:c r="I10" s="58" t="n">
         <x:f>IFERROR(C10*(E10-G10)/H10,"")</x:f>
-        <x:v>-0.33176070407799596</x:v>
+        <x:v>0.19144839185189863</x:v>
       </x:c>
       <x:c r="J10" s="58" t="n">
         <x:f>IF(I10="","",MAX(0,MIN(100,50+20*I10)))</x:f>
-        <x:v>43.36478591844008</x:v>
+        <x:v>53.82896783703797</x:v>
       </x:c>
       <x:c r="K10" s="54" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-10-22</x:v>
       </x:c>
       <x:c r="L10" s="54" t="n">
         <x:v>5</x:v>
@@ -2594,27 +2594,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E11" s="56" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.1200000000000001</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G11" s="56" t="n">
-        <x:v>-0.001538</x:v>
+        <x:v>0.006033003300330041</x:v>
       </x:c>
       <x:c r="H11" s="56" t="n">
-        <x:v>0.1527151</x:v>
+        <x:v>0.6962248922778974</x:v>
       </x:c>
       <x:c r="I11" s="58" t="n">
         <x:f>IFERROR(C11*(E11-G11)/H11,"")</x:f>
-        <x:v>0.2719966787829101</x:v>
+        <x:v>0.1636927923200141</x:v>
       </x:c>
       <x:c r="J11" s="58" t="n">
         <x:f>IF(I11="","",MAX(0,MIN(100,50+20*I11)))</x:f>
-        <x:v>55.4399335756582</x:v>
+        <x:v>53.27385584640028</x:v>
       </x:c>
       <x:c r="K11" s="54" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-10-22</x:v>
       </x:c>
       <x:c r="L11" s="54" t="n">
         <x:v>5</x:v>
@@ -2623,7 +2623,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N11" s="54" t="str">
-        <x:v>适合看边际再定价，不宜单独解释水平</x:v>
+        <x:v>适合看边际再定价</x:v>
       </x:c>
       <x:c r="O11" s="54" t="str">
         <x:v>FRED: T5YIE</x:v>
@@ -2643,27 +2643,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E12" s="56" t="n">
-        <x:v>2.31</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="F12" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G12" s="56" t="n">
-        <x:v>2.2678783</x:v>
+        <x:v>2.1613267326732686</x:v>
       </x:c>
       <x:c r="H12" s="56" t="n">
-        <x:v>0.0987903</x:v>
+        <x:v>0.4620256025114206</x:v>
       </x:c>
       <x:c r="I12" s="58" t="n">
         <x:f>IFERROR(C12*(E12-G12)/H12,"")</x:f>
-        <x:v>0.42637485664078395</x:v>
+        <x:v>0.06205991003717722</x:v>
       </x:c>
       <x:c r="J12" s="58" t="n">
         <x:f>IF(I12="","",MAX(0,MIN(100,50+20*I12)))</x:f>
-        <x:v>58.52749713281568</x:v>
+        <x:v>51.24119820074355</x:v>
       </x:c>
       <x:c r="K12" s="54" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-10-22</x:v>
       </x:c>
       <x:c r="L12" s="54" t="n">
         <x:v>5</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N12" s="54" t="str">
-        <x:v>长期锚；同样含风险与流动性成分</x:v>
+        <x:v>长期通胀锚，含风险与流动性成分</x:v>
       </x:c>
       <x:c r="O12" s="54" t="str">
         <x:v>FRED: T5YIFR</x:v>
@@ -2708,7 +2708,7 @@
       </x:c>
       <x:c r="J13" s="63" t="n">
         <x:f>SUMPRODUCT(D10:D12,J10:J12)/SUM(D10:D12)</x:f>
-        <x:v>52.139900962779095</x:v>
+        <x:v>52.85834774942646</x:v>
       </x:c>
       <x:c r="K13" s="64" t="str">
         <x:f>IF(J13&gt;=65,"高压",IF(J13&gt;=55,"偏紧",IF(J13&gt;=45,"中性",IF(J13&gt;=35,"偏松","宽松"))))</x:f>
@@ -2750,27 +2750,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E15" s="56" t="n">
-        <x:v>3.0857455</x:v>
+        <x:v>3.0245231607629375</x:v>
       </x:c>
       <x:c r="F15" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G15" s="56" t="n">
-        <x:v>4.3677958</x:v>
+        <x:v>4.286117534594615</x:v>
       </x:c>
       <x:c r="H15" s="56" t="n">
-        <x:v>0.6830206</x:v>
+        <x:v>0.8540343631541617</x:v>
       </x:c>
       <x:c r="I15" s="58" t="n">
         <x:f>IFERROR(C15*(E15-G15)/H15,"")</x:f>
-        <x:v>-1.8770302096305733</x:v>
+        <x:v>-1.4772173442439656</x:v>
       </x:c>
       <x:c r="J15" s="58" t="n">
         <x:f>IF(I15="","",MAX(0,MIN(100,50+20*I15)))</x:f>
-        <x:v>12.459395807388532</x:v>
+        <x:v>20.45565311512069</x:v>
       </x:c>
       <x:c r="K15" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L15" s="54" t="n">
         <x:v>5</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N15" s="54" t="str">
-        <x:v>月频、构成效应明显；CES会月度及年度修订</x:v>
+        <x:v>平均时薪同比；CES会月度及年度修订</x:v>
       </x:c>
       <x:c r="O15" s="54" t="str">
         <x:v>BLS/FRED: CES0500000003</x:v>
@@ -2848,27 +2848,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E17" s="56" t="n">
-        <x:v>4.1</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="F17" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G17" s="56" t="n">
-        <x:v>3.98</x:v>
+        <x:v>4.128985507246377</x:v>
       </x:c>
       <x:c r="H17" s="56" t="n">
-        <x:v>0.3550125</x:v>
+        <x:v>0.862469342895114</x:v>
       </x:c>
       <x:c r="I17" s="58" t="n">
         <x:f>IFERROR(C17*(E17-G17)/H17,"")</x:f>
-        <x:v>-0.33801626703285</x:v>
+        <x:v>-0.08233857045311783</x:v>
       </x:c>
       <x:c r="J17" s="58" t="n">
         <x:f>IF(I17="","",MAX(0,MIN(100,50+20*I17)))</x:f>
-        <x:v>43.239674659343</x:v>
+        <x:v>48.35322859093765</x:v>
       </x:c>
       <x:c r="K17" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L17" s="54" t="n">
         <x:v>5</x:v>
@@ -2877,7 +2877,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N17" s="54" t="str">
-        <x:v>家庭调查月频；样本波动大，单月变化需谨慎</x:v>
+        <x:v>家庭调查月频；单月变化需谨慎</x:v>
       </x:c>
       <x:c r="O17" s="54" t="str">
         <x:v>BLS/FRED: UNRATE</x:v>
@@ -2897,27 +2897,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E18" s="56" t="n">
-        <x:v>7271</x:v>
+        <x:v>7079</x:v>
       </x:c>
       <x:c r="F18" s="57" t="str">
         <x:v>千人</x:v>
       </x:c>
       <x:c r="G18" s="56" t="n">
-        <x:v>8847.2623</x:v>
+        <x:v>8822.54411764706</x:v>
       </x:c>
       <x:c r="H18" s="56" t="n">
-        <x:v>1750.1508</x:v>
+        <x:v>1702.9875367316663</x:v>
       </x:c>
       <x:c r="I18" s="58" t="n">
         <x:f>IFERROR(C18*(E18-G18)/H18,"")</x:f>
-        <x:v>-0.9006437045310612</x:v>
+        <x:v>-1.0238149604977311</x:v>
       </x:c>
       <x:c r="J18" s="58" t="n">
         <x:f>IF(I18="","",MAX(0,MIN(100,50+20*I18)))</x:f>
-        <x:v>31.987125909378776</x:v>
+        <x:v>29.52370079004538</x:v>
       </x:c>
       <x:c r="K18" s="54" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="L18" s="54" t="n">
         <x:v>5</x:v>
@@ -2926,7 +2926,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N18" s="54" t="str">
-        <x:v>并非高频；约1个月滞后、月度与年度修订较大</x:v>
+        <x:v>约1个月滞后，月度与年度修订较大</x:v>
       </x:c>
       <x:c r="O18" s="54" t="str">
         <x:v>BLS/FRED: JTSJOL</x:v>
@@ -2946,27 +2946,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E19" s="56" t="n">
-        <x:v>206000</x:v>
+        <x:v>197750</x:v>
       </x:c>
       <x:c r="F19" s="57" t="str">
         <x:v>人</x:v>
       </x:c>
       <x:c r="G19" s="56" t="n">
-        <x:v>223663.7931</x:v>
+        <x:v>264256.600660066</x:v>
       </x:c>
       <x:c r="H19" s="56" t="n">
-        <x:v>22445.2484</x:v>
+        <x:v>129218.31482708087</x:v>
       </x:c>
       <x:c r="I19" s="58" t="n">
         <x:f>IFERROR(C19*(E19-G19)/H19,"")</x:f>
-        <x:v>0.7869724934743877</x:v>
+        <x:v>0.5146840116980687</x:v>
       </x:c>
       <x:c r="J19" s="58" t="n">
         <x:f>IF(I19="","",MAX(0,MIN(100,50+20*I19)))</x:f>
-        <x:v>65.73944986948776</x:v>
+        <x:v>60.293680233961375</x:v>
       </x:c>
       <x:c r="K19" s="54" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>2026-10-17</x:v>
       </x:c>
       <x:c r="L19" s="54" t="n">
         <x:v>5</x:v>
@@ -2975,7 +2975,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N19" s="54" t="str">
-        <x:v>周频且及时；受季调、假期与州级申报扰动</x:v>
+        <x:v>周频四周均值；受季调、假期与州级申报扰动</x:v>
       </x:c>
       <x:c r="O19" s="54" t="str">
         <x:v>DOL/FRED: ICSA</x:v>
@@ -3011,11 +3011,11 @@
       </x:c>
       <x:c r="J20" s="63" t="n">
         <x:f>SUMPRODUCT(D15:D19,J15:J19)/SUM(D15:D19)</x:f>
-        <x:v>34.07851899065477</x:v>
+        <x:v>35.535065938131375</x:v>
       </x:c>
       <x:c r="K20" s="64" t="str">
         <x:f>IF(J20&gt;=65,"高压",IF(J20&gt;=55,"偏紧",IF(J20&gt;=45,"中性",IF(J20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>宽松</x:v>
+        <x:v>偏松</x:v>
       </x:c>
       <x:c r="L20" s="64"/>
       <x:c r="M20" s="64"/>
@@ -3053,27 +3053,27 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="E22" s="56" t="n">
-        <x:v>-0.7829083</x:v>
+        <x:v>3.3810311253439362</x:v>
       </x:c>
       <x:c r="F22" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G22" s="56" t="n">
-        <x:v>1.1590888</x:v>
+        <x:v>1.7052917625095732</x:v>
       </x:c>
       <x:c r="H22" s="56" t="n">
-        <x:v>3.0031765</x:v>
+        <x:v>3.23770758860311</x:v>
       </x:c>
       <x:c r="I22" s="58" t="n">
         <x:f>IFERROR(C22*(E22-G22)/H22,"")</x:f>
-        <x:v>-0.6466476745539265</x:v>
+        <x:v>0.5175697054091754</x:v>
       </x:c>
       <x:c r="J22" s="58" t="n">
         <x:f>IF(I22="","",MAX(0,MIN(100,50+20*I22)))</x:f>
-        <x:v>37.06704650892147</x:v>
+        <x:v>60.351394108183506</x:v>
       </x:c>
       <x:c r="K22" s="54" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L22" s="54" t="n">
         <x:v>5</x:v>
@@ -3082,7 +3082,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N22" s="54" t="str">
-        <x:v>广谱上游价格月频代理；不等于最终消费价格</x:v>
+        <x:v>广谱上游价格三个月变化，不等于最终消费价格</x:v>
       </x:c>
       <x:c r="O22" s="54" t="str">
         <x:v>BLS/FRED: PPIACO</x:v>
@@ -3102,27 +3102,27 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="E23" s="56" t="n">
-        <x:v>43.4199946</x:v>
+        <x:v>33.345692745025346</x:v>
       </x:c>
       <x:c r="F23" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G23" s="56" t="n">
-        <x:v>2.3565562</x:v>
+        <x:v>0.1672936971689474</x:v>
       </x:c>
       <x:c r="H23" s="56" t="n">
-        <x:v>19.3365269</x:v>
+        <x:v>28.649142075049937</x:v>
       </x:c>
       <x:c r="I23" s="58" t="n">
         <x:f>IFERROR(C23*(E23-G23)/H23,"")</x:f>
-        <x:v>2.123620162625999</x:v>
+        <x:v>1.1580939827427124</x:v>
       </x:c>
       <x:c r="J23" s="58" t="n">
         <x:f>IF(I23="","",MAX(0,MIN(100,50+20*I23)))</x:f>
-        <x:v>92.47240325251998</x:v>
+        <x:v>73.16187965485425</x:v>
       </x:c>
       <x:c r="K23" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L23" s="54" t="n">
         <x:v>5</x:v>
@@ -3131,7 +3131,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N23" s="54" t="str">
-        <x:v>高频且准确反映能源；不能代表核心服务通胀</x:v>
+        <x:v>高频能源价格变化，不能代表核心服务通胀</x:v>
       </x:c>
       <x:c r="O23" s="54" t="str">
         <x:v>EIA/FRED: DCOILWTICO</x:v>
@@ -3167,7 +3167,7 @@
       </x:c>
       <x:c r="J24" s="63" t="n">
         <x:f>SUMPRODUCT(D22:D23,J22:J23)/SUM(D22:D23)</x:f>
-        <x:v>73.0805283922605</x:v>
+        <x:v>68.6782097135195</x:v>
       </x:c>
       <x:c r="K24" s="64" t="str">
         <x:f>IF(J24&gt;=65,"高压",IF(J24&gt;=55,"偏紧",IF(J24&gt;=45,"中性",IF(J24&gt;=35,"偏松","宽松"))))</x:f>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>50.00654275843186</x:v>
+        <x:v>49.95917150829179</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3267,27 +3267,27 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E28" s="56" t="n">
-        <x:v>0.729847215978831</x:v>
+        <x:v>0.718008053968759</x:v>
       </x:c>
       <x:c r="F28" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G28" s="56" t="n">
-        <x:v>-0.048298865819274124</x:v>
+        <x:v>-0.0477707425113568</x:v>
       </x:c>
       <x:c r="H28" s="56" t="n">
-        <x:v>0.5488544542960424</x:v>
+        <x:v>0.5490338459384495</x:v>
       </x:c>
       <x:c r="I28" s="58" t="n">
         <x:f>IFERROR(C28*(E28-G28)/H28,"")</x:f>
-        <x:v>1.4177639913593318</x:v>
+        <x:v>1.394775207658081</x:v>
       </x:c>
       <x:c r="J28" s="58" t="n">
         <x:f>IF(I28="","",MAX(0,MIN(100,50+20*I28)))</x:f>
-        <x:v>78.35527982718664</x:v>
+        <x:v>77.89550415316162</x:v>
       </x:c>
       <x:c r="K28" s="54" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L28" s="54" t="n">
         <x:v>5</x:v>
@@ -3316,27 +3316,27 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="E29" s="56" t="n">
-        <x:v>0.15400760358896093</x:v>
+        <x:v>0.14629031404763104</x:v>
       </x:c>
       <x:c r="F29" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G29" s="56" t="n">
-        <x:v>0.022759995492742695</x:v>
+        <x:v>0.022845130102360126</x:v>
       </x:c>
       <x:c r="H29" s="56" t="n">
-        <x:v>0.22599946658696593</x:v>
+        <x:v>0.2259447962262693</x:v>
       </x:c>
       <x:c r="I29" s="58" t="n">
         <x:f>IFERROR(C29*(E29-G29)/H29,"")</x:f>
-        <x:v>0.5807429994340867</x:v>
+        <x:v>0.5463510822424449</x:v>
       </x:c>
       <x:c r="J29" s="58" t="n">
         <x:f>IF(I29="","",MAX(0,MIN(100,50+20*I29)))</x:f>
-        <x:v>61.61485998868173</x:v>
+        <x:v>60.9270216448489</x:v>
       </x:c>
       <x:c r="K29" s="54" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L29" s="54" t="n">
         <x:v>5</x:v>
@@ -3381,7 +3381,7 @@
       </x:c>
       <x:c r="J30" s="63" t="n">
         <x:f>SUMPRODUCT(D28:D29,J28:J29)/SUM(D28:D29)</x:f>
-        <x:v>73.33315387563516</x:v>
+        <x:v>72.8049594006678</x:v>
       </x:c>
       <x:c r="K30" s="64" t="str">
         <x:f>IF(J30&gt;=65,"高压",IF(J30&gt;=55,"偏紧",IF(J30&gt;=45,"中性",IF(J30&gt;=35,"偏松","宽松"))))</x:f>
@@ -3423,27 +3423,27 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E32" s="56" t="n">
-        <x:v>0.28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G32" s="56" t="n">
-        <x:v>0.038659</x:v>
+        <x:v>0.04836856010568032</x:v>
       </x:c>
       <x:c r="H32" s="56" t="n">
-        <x:v>0.1966126</x:v>
+        <x:v>0.5119650144654966</x:v>
       </x:c>
       <x:c r="I32" s="58" t="n">
         <x:f>IFERROR(C32*(E32-G32)/H32,"")</x:f>
-        <x:v>1.2274950842418035</x:v>
+        <x:v>-0.09447629962797013</x:v>
       </x:c>
       <x:c r="J32" s="58" t="n">
         <x:f>IF(I32="","",MAX(0,MIN(100,50+20*I32)))</x:f>
-        <x:v>74.54990168483607</x:v>
+        <x:v>48.1104740074406</x:v>
       </x:c>
       <x:c r="K32" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L32" s="54" t="n">
         <x:v>5</x:v>
@@ -3472,27 +3472,27 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="E33" s="56" t="n">
-        <x:v>0.13</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G33" s="56" t="n">
-        <x:v>-0.025786</x:v>
+        <x:v>-0.027441860465116222</x:v>
       </x:c>
       <x:c r="H33" s="56" t="n">
-        <x:v>0.2641338</x:v>
+        <x:v>0.5368757964435378</x:v>
       </x:c>
       <x:c r="I33" s="58" t="n">
         <x:f>IFERROR(C33*(E33-G33)/H33,"")</x:f>
-        <x:v>0.5897995637059703</x:v>
+        <x:v>1.0569332129033555</x:v>
       </x:c>
       <x:c r="J33" s="58" t="n">
         <x:f>IF(I33="","",MAX(0,MIN(100,50+20*I33)))</x:f>
-        <x:v>61.7959912741194</x:v>
+        <x:v>71.13866425806711</x:v>
       </x:c>
       <x:c r="K33" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L33" s="54" t="n">
         <x:v>5</x:v>
@@ -3521,27 +3521,27 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E34" s="56" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.10999999999999999</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
         <x:v>百分点</x:v>
       </x:c>
       <x:c r="G34" s="56" t="n">
-        <x:v>-0.0080372</x:v>
+        <x:v>-0.011395348837209334</x:v>
       </x:c>
       <x:c r="H34" s="56" t="n">
-        <x:v>0.0636386</x:v>
+        <x:v>0.1543801738038932</x:v>
       </x:c>
       <x:c r="I34" s="58" t="n">
         <x:f>IFERROR(C34*(E34-G34)/H34,"")</x:f>
-        <x:v>0.2834317536840848</x:v>
+        <x:v>0.7863402783275525</x:v>
       </x:c>
       <x:c r="J34" s="58" t="n">
         <x:f>IF(I34="","",MAX(0,MIN(100,50+20*I34)))</x:f>
-        <x:v>55.6686350736817</x:v>
+        <x:v>65.72680556655105</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L34" s="54" t="n">
         <x:v>5</x:v>
@@ -3550,7 +3550,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N34" s="54" t="str">
-        <x:v>比高收益更稳健，但对早期风险反应较弱</x:v>
+        <x:v>投资级信用条件确认指标</x:v>
       </x:c>
       <x:c r="O34" s="54" t="str">
         <x:v>FRED: BAMLC0A0CM</x:v>
@@ -3570,27 +3570,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E35" s="56" t="n">
-        <x:v>17.2</x:v>
+        <x:v>16.68</x:v>
       </x:c>
       <x:c r="F35" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G35" s="56" t="n">
-        <x:v>19.129697</x:v>
+        <x:v>18.837602377807123</x:v>
       </x:c>
       <x:c r="H35" s="56" t="n">
-        <x:v>5.2749403</x:v>
+        <x:v>5.578125308215269</x:v>
       </x:c>
       <x:c r="I35" s="58" t="n">
         <x:f>IFERROR(C35*(E35-G35)/H35,"")</x:f>
-        <x:v>-0.36582347671309207</x:v>
+        <x:v>-0.3867970435568167</x:v>
       </x:c>
       <x:c r="J35" s="58" t="n">
         <x:f>IF(I35="","",MAX(0,MIN(100,50+20*I35)))</x:f>
-        <x:v>42.68353046573816</x:v>
+        <x:v>42.264059128863664</x:v>
       </x:c>
       <x:c r="K35" s="54" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-10-21</x:v>
       </x:c>
       <x:c r="L35" s="54" t="n">
         <x:v>5</x:v>
@@ -3619,27 +3619,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E36" s="56" t="n">
-        <x:v>-0.1231008</x:v>
+        <x:v>1.5826690418555778</x:v>
       </x:c>
       <x:c r="F36" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G36" s="56" t="n">
-        <x:v>0.0573589</x:v>
+        <x:v>-3.8932762266238274</x:v>
       </x:c>
       <x:c r="H36" s="56" t="n">
-        <x:v>1.1875496</x:v>
+        <x:v>19.693125027432618</x:v>
       </x:c>
       <x:c r="I36" s="58" t="n">
         <x:f>IFERROR(C36*(E36-G36)/H36,"")</x:f>
-        <x:v>-0.1519597160404921</x:v>
+        <x:v>0.2780638045435342</x:v>
       </x:c>
       <x:c r="J36" s="58" t="n">
         <x:f>IF(I36="","",MAX(0,MIN(100,50+20*I36)))</x:f>
-        <x:v>46.96080567919016</x:v>
+        <x:v>55.561276090870685</x:v>
       </x:c>
       <x:c r="K36" s="54" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L36" s="54" t="n">
         <x:v>5</x:v>
@@ -3668,27 +3668,27 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="E37" s="56" t="n">
-        <x:v>-0.56</x:v>
+        <x:v>-0.496</x:v>
       </x:c>
       <x:c r="F37" s="57" t="str">
         <x:v>指数</x:v>
       </x:c>
       <x:c r="G37" s="56" t="n">
-        <x:v>-0.3977854</x:v>
+        <x:v>-0.4309405940594058</x:v>
       </x:c>
       <x:c r="H37" s="56" t="n">
-        <x:v>0.1335983</x:v>
+        <x:v>0.15369841169401138</x:v>
       </x:c>
       <x:c r="I37" s="58" t="n">
         <x:f>IFERROR(C37*(E37-G37)/H37,"")</x:f>
-        <x:v>-1.2141965878308334</x:v>
+        <x:v>-0.42329263668720857</x:v>
       </x:c>
       <x:c r="J37" s="58" t="n">
         <x:f>IF(I37="","",MAX(0,MIN(100,50+20*I37)))</x:f>
-        <x:v>25.716068243383333</x:v>
+        <x:v>41.53414726625583</x:v>
       </x:c>
       <x:c r="K37" s="54" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="L37" s="54" t="n">
         <x:v>5</x:v>
@@ -3697,7 +3697,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N37" s="54" t="str">
-        <x:v>周频综合金融条件；负值代表较历史均值宽松</x:v>
+        <x:v>周频综合金融条件；负值代表相对宽松</x:v>
       </x:c>
       <x:c r="O37" s="54" t="str">
         <x:v>Chicago Fed/FRED: NFCI</x:v>
@@ -3733,7 +3733,7 @@
       </x:c>
       <x:c r="J38" s="63" t="n">
         <x:f>SUMPRODUCT(D32:D37,J32:J37)/SUM(D32:D37)</x:f>
-        <x:v>53.867597841647815</x:v>
+        <x:v>53.73195428302721</x:v>
       </x:c>
       <x:c r="K38" s="64" t="str">
         <x:f>IF(J38&gt;=65,"高压",IF(J38&gt;=55,"偏紧",IF(J38&gt;=45,"中性",IF(J38&gt;=35,"偏松","宽松"))))</x:f>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="B42" s="58" t="n">
         <x:f>J8</x:f>
-        <x:v>74.83655499836406</x:v>
+        <x:v>57.22829360240057</x:v>
       </x:c>
       <x:c r="C42" s="54" t="str">
         <x:v>0-100，越高越收紧</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>50.00654275843186</x:v>
+        <x:v>49.95917150829179</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="B44" s="58" t="n">
         <x:f>J30</x:f>
-        <x:v>73.33315387563516</x:v>
+        <x:v>72.8049594006678</x:v>
       </x:c>
       <x:c r="C44" s="54" t="str">
         <x:v>ACM水平70%+20日变化30%</x:v>
@@ -3919,7 +3919,7 @@
       </x:c>
       <x:c r="B45" s="58" t="n">
         <x:f>J38</x:f>
-        <x:v>53.867597841647815</x:v>
+        <x:v>53.73195428302721</x:v>
       </x:c>
       <x:c r="C45" s="54" t="str">
         <x:v>实际利率+信用+波动率+美元+NFCI</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>65.69503037756913</x:v>
+        <x:v>59.35710060894266</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>66.9654401660455</x:v>
+        <x:v>60.46469053817076</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>58.16284261855763</x:v>
+        <x:v>57.944742708425224</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.7526366173917118</x:v>
+        <x:v>0.47639071404866157</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.24736338260828816</x:v>
+        <x:v>0.5236092859513384</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4127,7 +4127,7 @@
       </x:c>
       <x:c r="B53" s="68" t="str">
         <x:f>IF(AND(B42&gt;=60,B44&gt;=60,B43&lt;60),"政策重定价 + 期限溢价冲击",IF(AND(B46&gt;=65,B45&gt;=60),"全面收紧传导",IF(AND(B43&gt;=60,B44&gt;=60),"通胀与期限溢价共振",IF(AND(B42&gt;=60,B43&lt;55,B45&lt;55),"政策独涨/预防性加息",IF(AND(B46&lt;=40,B45&lt;=45),"宽松传导","混合状态")))))</x:f>
-        <x:v>政策重定价 + 期限溢价冲击</x:v>
+        <x:v>混合状态</x:v>
       </x:c>
       <x:c r="C53" s="68" t="str">
         <x:v>规则优先于主观叙事</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>36.061324041649556</x:v>
+        <x:v>40.78190734974757</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>36.42170776786702</x:v>
+        <x:v>40.8430394023309</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>36.88665337721134</x:v>
+        <x:v>42.258986122741376</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>37.66328142005268</x:v>
+        <x:v>42.38848017160706</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>37.86196498323582</x:v>
+        <x:v>41.951299318883656</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>38.12621889545232</x:v>
+        <x:v>42.65079341806066</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>35.55160686222782</x:v>
+        <x:v>40.764492188550186</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,11 +4572,11 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>43.65430684184569</x:v>
+        <x:v>45.78407918986468</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
-        <x:v>偏不利</x:v>
+        <x:v>中性</x:v>
       </x:c>
       <x:c r="H13" s="54" t="str">
         <x:v>通胀与实物供需</x:v>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>35.65907255968799</x:v>
+        <x:v>39.619700514709706</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>63.85300652527993</x:v>
+        <x:v>58.06173864479713</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4844,43 +4844,43 @@
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'因子引擎'!$B$42</x:f>
-        <x:v>74.83655499836406</x:v>
+        <x:v>57.22829360240057</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>50.00654275843186</x:v>
+        <x:v>49.95917150829179</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
-        <x:v>73.33315387563516</x:v>
+        <x:v>72.8049594006678</x:v>
       </x:c>
       <x:c r="E6" s="58" t="n">
         <x:f>'因子引擎'!$B$45</x:f>
-        <x:v>53.867597841647815</x:v>
+        <x:v>53.73195428302721</x:v>
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>66.9654401660455</x:v>
+        <x:v>60.46469053817076</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>36.061324041649556</x:v>
+        <x:v>40.78190734974757</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>36.42170776786702</x:v>
+        <x:v>40.8430394023309</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>37.66328142005268</x:v>
+        <x:v>42.38848017160706</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>38.12621889545232</x:v>
+        <x:v>42.65079341806066</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>63.85300652527993</x:v>
+        <x:v>58.06173864479713</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>66.9654401660455</x:v>
+        <x:v>60.46469053817076</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>35.55160686222782</x:v>
+        <x:v>39.619700514709706</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Re4f4d76ef8b348b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R70c0be9ed9e645af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R2f00e376ec89412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R78832e063adc47f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rc435d777cd4c42b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R2484796737584f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R6f6c6938cf014b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Rad0be1389c4444e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R19cb2779bc0341a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rd5fc300349654dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rcac17792e93a457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R3163750e9e4b4058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R1a18343be299468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R248bfebb55f84f4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbaa0d9f96026448d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7fc152484c0348e9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R640023285cbc4aff"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cfa1b2389394023"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1238,7 +1238,7 @@
       <x:c r="C6" s="99"/>
       <x:c r="D6" s="99" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>49.95917150829179</x:v>
+        <x:v>47.08238984612924</x:v>
       </x:c>
       <x:c r="E6" s="99"/>
       <x:c r="F6" s="99"/>
@@ -1256,7 +1256,7 @@
       <x:c r="L6" s="99"/>
       <x:c r="M6" s="99" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.46469053817076</x:v>
+        <x:v>59.439028925534345</x:v>
       </x:c>
       <x:c r="N6" s="99"/>
       <x:c r="O6" s="99"/>
@@ -1420,7 +1420,7 @@
       </x:c>
       <x:c r="J12" s="50" t="n">
         <x:f>'因子引擎'!$B$49</x:f>
-        <x:v>0.47639071404866157</x:v>
+        <x:v>0.515484721712491</x:v>
       </x:c>
       <x:c r="K12" s="50" t="str">
         <x:v>主导</x:v>
@@ -1430,7 +1430,7 @@
       </x:c>
       <x:c r="M12" s="50" t="n">
         <x:f>'因子引擎'!$B$50</x:f>
-        <x:v>0.5236092859513384</x:v>
+        <x:v>0.48451527828750895</x:v>
       </x:c>
       <x:c r="N12" s="39" t="str">
         <x:v>未完全确认</x:v>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>49.95917150829179</x:v>
+        <x:v>47.08238984612924</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:f>IF(B21&gt;=65,"高压",IF(B21&gt;=55,"偏紧",IF(B21&gt;=45,"中性",IF(B21&gt;=35,"偏松","宽松"))))</x:f>
@@ -1718,7 +1718,7 @@
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:f>'因子引擎'!$B$47</x:f>
-        <x:v>60.46469053817076</x:v>
+        <x:v>59.439028925534345</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:f>IF(B24&gt;=65,"高压",IF(B24&gt;=55,"偏紧",IF(B24&gt;=45,"中性",IF(B24&gt;=35,"偏松","宽松"))))</x:f>
@@ -1767,7 +1767,7 @@
       </x:c>
       <x:c r="B29" s="43" t="n">
         <x:f>'风险资产'!$F$6</x:f>
-        <x:v>40.78190734974757</x:v>
+        <x:v>41.43945744395615</x:v>
       </x:c>
       <x:c r="C29" s="39" t="str">
         <x:f>'风险资产'!$G$6</x:f>
@@ -1780,7 +1780,7 @@
       </x:c>
       <x:c r="B30" s="43" t="n">
         <x:f>'风险资产'!$F$7</x:f>
-        <x:v>40.8430394023309</x:v>
+        <x:v>41.418395734763415</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:f>'风险资产'!$G$7</x:f>
@@ -1793,7 +1793,7 @@
       </x:c>
       <x:c r="B31" s="43" t="n">
         <x:f>'风险资产'!$F$8</x:f>
-        <x:v>42.258986122741376</x:v>
+        <x:v>42.68517599861731</x:v>
       </x:c>
       <x:c r="C31" s="39" t="str">
         <x:f>'风险资产'!$G$8</x:f>
@@ -1806,7 +1806,7 @@
       </x:c>
       <x:c r="B32" s="43" t="n">
         <x:f>'风险资产'!$F$9</x:f>
-        <x:v>42.38848017160706</x:v>
+        <x:v>42.81467004748299</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:f>'风险资产'!$G$9</x:f>
@@ -1819,7 +1819,7 @@
       </x:c>
       <x:c r="B33" s="43" t="n">
         <x:f>'风险资产'!$F$10</x:f>
-        <x:v>41.951299318883656</x:v>
+        <x:v>42.484036663728574</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:f>'风险资产'!$G$10</x:f>
@@ -1832,7 +1832,7 @@
       </x:c>
       <x:c r="B34" s="43" t="n">
         <x:f>'风险资产'!$F$11</x:f>
-        <x:v>42.65079341806066</x:v>
+        <x:v>41.69186619733981</x:v>
       </x:c>
       <x:c r="C34" s="39" t="str">
         <x:f>'风险资产'!$G$11</x:f>
@@ -1845,7 +1845,7 @@
       </x:c>
       <x:c r="B35" s="43" t="n">
         <x:f>'风险资产'!$F$12</x:f>
-        <x:v>40.764492188550186</x:v>
+        <x:v>40.55900778411</x:v>
       </x:c>
       <x:c r="C35" s="39" t="str">
         <x:f>'风险资产'!$G$12</x:f>
@@ -1858,11 +1858,11 @@
       </x:c>
       <x:c r="B36" s="43" t="n">
         <x:f>'风险资产'!$F$13</x:f>
-        <x:v>45.78407918986468</x:v>
+        <x:v>44.091854682710235</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:f>'风险资产'!$G$13</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏不利</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
@@ -1871,7 +1871,7 @@
       </x:c>
       <x:c r="B37" s="43" t="n">
         <x:f>'风险资产'!$F$14</x:f>
-        <x:v>39.619700514709706</x:v>
+        <x:v>40.40427733166313</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
         <x:f>'风险资产'!$G$14</x:f>
@@ -1884,7 +1884,7 @@
       </x:c>
       <x:c r="B38" s="43" t="n">
         <x:f>'风险资产'!$F$15</x:f>
-        <x:v>58.06173864479713</x:v>
+        <x:v>57.60145357885113</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:f>'风险资产'!$G$15</x:f>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27057fb4ed8f4b02"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffa5d523652145d4"/>
 </x:worksheet>
 </file>
 
@@ -2369,7 +2369,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N5" s="54" t="str">
-        <x:v>2Y与有效联邦基金利率之差，包含2Y期限溢价</x:v>
+        <x:v>2Y与有效联邦基金利率之差，包含2Y期限溢价；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O5" s="54" t="str">
         <x:v>FRED: DGS2-DFF</x:v>
@@ -2418,7 +2418,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="54" t="str">
-        <x:v>捕捉政策路径重定价</x:v>
+        <x:v>捕捉政策路径重定价；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O6" s="54" t="str">
         <x:v>FRED: DGS2</x:v>
@@ -2467,7 +2467,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N7" s="54" t="str">
-        <x:v>实际政策动作，离散且滞后于市场定价</x:v>
+        <x:v>实际政策动作，离散且滞后于市场定价；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O7" s="54" t="str">
         <x:v>FRED: DFF</x:v>
@@ -2574,7 +2574,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N10" s="54" t="str">
-        <x:v>含通胀风险与TIPS流动性溢价，不是纯预期</x:v>
+        <x:v>含通胀风险与TIPS流动性溢价，不是纯预期；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O10" s="54" t="str">
         <x:v>FRED: T5YIE</x:v>
@@ -2623,7 +2623,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N11" s="54" t="str">
-        <x:v>适合看边际再定价</x:v>
+        <x:v>适合看边际再定价；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O11" s="54" t="str">
         <x:v>FRED: T5YIE</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N12" s="54" t="str">
-        <x:v>长期通胀锚，含风险与流动性成分</x:v>
+        <x:v>长期通胀锚，含风险与流动性成分；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O12" s="54" t="str">
         <x:v>FRED: T5YIFR</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N15" s="54" t="str">
-        <x:v>平均时薪同比；CES会月度及年度修订</x:v>
+        <x:v>平均时薪同比；CES会月度及年度修订；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O15" s="54" t="str">
         <x:v>BLS/FRED: CES0500000003</x:v>
@@ -2799,36 +2799,36 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="E16" s="56" t="n">
-        <x:v>3.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="57" t="str">
         <x:v>%</x:v>
       </x:c>
       <x:c r="G16" s="56" t="n">
-        <x:v>4.776470588235295</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="H16" s="56" t="n">
-        <x:v>1.0237650218763872</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="I16" s="58" t="n">
         <x:f>IFERROR(C16*(E16-G16)/H16,"")</x:f>
-        <x:v>-0.8561247644785456</x:v>
+        <x:v>-3.3333333333333335</x:v>
       </x:c>
       <x:c r="J16" s="58" t="n">
         <x:f>IF(I16="","",MAX(0,MIN(100,50+20*I16)))</x:f>
-        <x:v>32.87750471042909</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="54" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L16" s="54" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M16" s="54" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="N16" s="54" t="str">
-        <x:v>匹配同一劳动者的工资增速；官方三个月移动平均序列</x:v>
+        <x:v>Atlanta Fed匹配同一劳动者的工资增速；页面字段自动识别；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O16" s="54" t="str">
         <x:v>Atlanta Fed WGT</x:v>
@@ -2877,7 +2877,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N17" s="54" t="str">
-        <x:v>家庭调查月频；单月变化需谨慎</x:v>
+        <x:v>家庭调查月频；单月变化需谨慎；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O17" s="54" t="str">
         <x:v>BLS/FRED: UNRATE</x:v>
@@ -2926,7 +2926,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N18" s="54" t="str">
-        <x:v>约1个月滞后，月度与年度修订较大</x:v>
+        <x:v>约1个月滞后，月度与年度修订较大；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O18" s="54" t="str">
         <x:v>BLS/FRED: JTSJOL</x:v>
@@ -2975,7 +2975,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N19" s="54" t="str">
-        <x:v>周频四周均值；受季调、假期与州级申报扰动</x:v>
+        <x:v>周频四周均值；受季调、假期与州级申报扰动；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O19" s="54" t="str">
         <x:v>DOL/FRED: ICSA</x:v>
@@ -3011,11 +3011,11 @@
       </x:c>
       <x:c r="J20" s="63" t="n">
         <x:f>SUMPRODUCT(D15:D19,J15:J19)/SUM(D15:D19)</x:f>
-        <x:v>35.535065938131375</x:v>
+        <x:v>27.3156897605241</x:v>
       </x:c>
       <x:c r="K20" s="64" t="str">
         <x:f>IF(J20&gt;=65,"高压",IF(J20&gt;=55,"偏紧",IF(J20&gt;=45,"中性",IF(J20&gt;=35,"偏松","宽松"))))</x:f>
-        <x:v>偏松</x:v>
+        <x:v>宽松</x:v>
       </x:c>
       <x:c r="L20" s="64"/>
       <x:c r="M20" s="64"/>
@@ -3082,7 +3082,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N22" s="54" t="str">
-        <x:v>广谱上游价格三个月变化，不等于最终消费价格</x:v>
+        <x:v>广谱上游价格三个月变化，不等于最终消费价格；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O22" s="54" t="str">
         <x:v>BLS/FRED: PPIACO</x:v>
@@ -3131,7 +3131,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N23" s="54" t="str">
-        <x:v>高频能源价格变化，不能代表核心服务通胀</x:v>
+        <x:v>高频能源价格变化，不能代表核心服务通胀；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O23" s="54" t="str">
         <x:v>EIA/FRED: DCOILWTICO</x:v>
@@ -3225,7 +3225,7 @@
       </x:c>
       <x:c r="J26" s="63" t="n">
         <x:f>45%*J13+35%*J20+20%*J24</x:f>
-        <x:v>49.95917150829179</x:v>
+        <x:v>47.08238984612924</x:v>
       </x:c>
       <x:c r="K26" s="64" t="str">
         <x:f>IF(J26&gt;=65,"高压",IF(J26&gt;=55,"偏紧",IF(J26&gt;=45,"中性",IF(J26&gt;=35,"偏松","宽松"))))</x:f>
@@ -3296,7 +3296,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N28" s="54" t="str">
-        <x:v>模型估计值；存在模型风险</x:v>
+        <x:v>模型估计值；存在模型风险；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O28" s="54" t="str">
         <x:v>NY Fed ACMTP10</x:v>
@@ -3345,7 +3345,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N29" s="54" t="str">
-        <x:v>判断长端上行是否来自期限溢价边际扩张</x:v>
+        <x:v>判断长端上行是否来自期限溢价边际扩张；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O29" s="54" t="str">
         <x:v>NY Fed ACMTP10</x:v>
@@ -3452,7 +3452,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N32" s="54" t="str">
-        <x:v>长久期估值的直接折现率通道</x:v>
+        <x:v>长久期估值的直接折现率通道；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O32" s="54" t="str">
         <x:v>FRED: DFII10</x:v>
@@ -3501,7 +3501,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N33" s="54" t="str">
-        <x:v>信用风险与融资条件核心确认指标</x:v>
+        <x:v>信用风险与融资条件核心确认指标；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O33" s="54" t="str">
         <x:v>FRED: BAMLH0A0HYM2</x:v>
@@ -3550,7 +3550,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N34" s="54" t="str">
-        <x:v>投资级信用条件确认指标</x:v>
+        <x:v>投资级信用条件确认指标；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O34" s="54" t="str">
         <x:v>FRED: BAMLC0A0CM</x:v>
@@ -3599,7 +3599,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N35" s="54" t="str">
-        <x:v>股票隐含波动；事件冲击快、均值回归也快</x:v>
+        <x:v>股票隐含波动；事件冲击快、均值回归也快；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O35" s="54" t="str">
         <x:v>CBOE/FRED: VIXCLS</x:v>
@@ -3648,7 +3648,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N36" s="54" t="str">
-        <x:v>全球美元流动性与风险偏好代理</x:v>
+        <x:v>全球美元流动性与风险偏好代理；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O36" s="54" t="str">
         <x:v>Fed/FRED: DTWEXBGS</x:v>
@@ -3697,7 +3697,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N37" s="54" t="str">
-        <x:v>周频综合金融条件；负值代表相对宽松</x:v>
+        <x:v>周频综合金融条件；负值代表相对宽松；本次来源未更新，沿用上一有效值</x:v>
       </x:c>
       <x:c r="O37" s="54" t="str">
         <x:v>Chicago Fed/FRED: NFCI</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="B43" s="58" t="n">
         <x:f>J26</x:f>
-        <x:v>49.95917150829179</x:v>
+        <x:v>47.08238984612924</x:v>
       </x:c>
       <x:c r="C43" s="54" t="str">
         <x:v>市场预期45%+工资劳动力35%+原材料20%</x:v>
@@ -3945,7 +3945,7 @@
       </x:c>
       <x:c r="B46" s="58" t="n">
         <x:f>35%*B42+35%*B43+30%*B44</x:f>
-        <x:v>59.35710060894266</x:v>
+        <x:v>58.35022702718577</x:v>
       </x:c>
       <x:c r="C46" s="54" t="str">
         <x:v>政策35%+通胀35%+期限溢价30%</x:v>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c r="B47" s="58" t="n">
         <x:f>MIN(100,MAX(0,B46*(0.75+0.5*B45/100)))</x:f>
-        <x:v>60.46469053817076</x:v>
+        <x:v>59.439028925534345</x:v>
       </x:c>
       <x:c r="C47" s="54" t="str">
         <x:v>基础压力×(0.75+0.5×传导/100)</x:v>
@@ -3997,7 +3997,7 @@
       </x:c>
       <x:c r="B48" s="58" t="n">
         <x:f>40%*B43+30%*B44+30%*B45</x:f>
-        <x:v>57.944742708425224</x:v>
+        <x:v>56.7940300435602</x:v>
       </x:c>
       <x:c r="C48" s="54" t="str">
         <x:v>通胀40%+期限30%+传导30%</x:v>
@@ -4023,7 +4023,7 @@
       </x:c>
       <x:c r="B49" s="67" t="n">
         <x:f>IFERROR(ABS(B42-50)/(ABS(B42-50)+ABS(B48-50)),50%)</x:f>
-        <x:v>0.47639071404866157</x:v>
+        <x:v>0.515484721712491</x:v>
       </x:c>
       <x:c r="C49" s="54" t="str">
         <x:v>|政策-50|÷(|政策-50|+|市场-50|)</x:v>
@@ -4049,7 +4049,7 @@
       </x:c>
       <x:c r="B50" s="67" t="n">
         <x:f>1-B49</x:f>
-        <x:v>0.5236092859513384</x:v>
+        <x:v>0.48451527828750895</x:v>
       </x:c>
       <x:c r="C50" s="54" t="str">
         <x:v>1-政策冲击占比</x:v>
@@ -4101,7 +4101,7 @@
       </x:c>
       <x:c r="B52" s="58" t="n">
         <x:f>AVERAGE(L5:L7,L10:L12,L15:L19,L22:L23,L28:L29,L32:L37)*10+AVERAGE(M5:M7,M10:M12,M15:M19,M22:M23,M28:M29,M32:M37)*10</x:f>
-        <x:v>89.04761904761904</x:v>
+        <x:v>88.57142857142857</x:v>
       </x:c>
       <x:c r="C52" s="54" t="str">
         <x:v>可得性与准确性均值</x:v>
@@ -4334,7 +4334,7 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6*('因子引擎'!$B$42-50))+(C6*('因子引擎'!$B$43-50))+(D6*('因子引擎'!$B$44-50))+(E6*('因子引擎'!$B$45-50)))/(ABS(B6)+ABS(C6)+ABS(D6)+ABS(E6))))</x:f>
-        <x:v>40.78190734974757</x:v>
+        <x:v>41.43945744395615</x:v>
       </x:c>
       <x:c r="G6" s="54" t="str">
         <x:f>IF(F6&gt;=65,"明显有利",IF(F6&gt;=55,"偏有利",IF(F6&gt;=45,"中性",IF(F6&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="F7" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B7*('因子引擎'!$B$42-50))+(C7*('因子引擎'!$B$43-50))+(D7*('因子引擎'!$B$44-50))+(E7*('因子引擎'!$B$45-50)))/(ABS(B7)+ABS(C7)+ABS(D7)+ABS(E7))))</x:f>
-        <x:v>40.8430394023309</x:v>
+        <x:v>41.418395734763415</x:v>
       </x:c>
       <x:c r="G7" s="54" t="str">
         <x:f>IF(F7&gt;=65,"明显有利",IF(F7&gt;=55,"偏有利",IF(F7&gt;=45,"中性",IF(F7&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4402,7 +4402,7 @@
       </x:c>
       <x:c r="F8" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B8*('因子引擎'!$B$42-50))+(C8*('因子引擎'!$B$43-50))+(D8*('因子引擎'!$B$44-50))+(E8*('因子引擎'!$B$45-50)))/(ABS(B8)+ABS(C8)+ABS(D8)+ABS(E8))))</x:f>
-        <x:v>42.258986122741376</x:v>
+        <x:v>42.68517599861731</x:v>
       </x:c>
       <x:c r="G8" s="54" t="str">
         <x:f>IF(F8&gt;=65,"明显有利",IF(F8&gt;=55,"偏有利",IF(F8&gt;=45,"中性",IF(F8&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4436,7 +4436,7 @@
       </x:c>
       <x:c r="F9" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B9*('因子引擎'!$B$42-50))+(C9*('因子引擎'!$B$43-50))+(D9*('因子引擎'!$B$44-50))+(E9*('因子引擎'!$B$45-50)))/(ABS(B9)+ABS(C9)+ABS(D9)+ABS(E9))))</x:f>
-        <x:v>42.38848017160706</x:v>
+        <x:v>42.81467004748299</x:v>
       </x:c>
       <x:c r="G9" s="54" t="str">
         <x:f>IF(F9&gt;=65,"明显有利",IF(F9&gt;=55,"偏有利",IF(F9&gt;=45,"中性",IF(F9&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4470,7 +4470,7 @@
       </x:c>
       <x:c r="F10" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B10*('因子引擎'!$B$42-50))+(C10*('因子引擎'!$B$43-50))+(D10*('因子引擎'!$B$44-50))+(E10*('因子引擎'!$B$45-50)))/(ABS(B10)+ABS(C10)+ABS(D10)+ABS(E10))))</x:f>
-        <x:v>41.951299318883656</x:v>
+        <x:v>42.484036663728574</x:v>
       </x:c>
       <x:c r="G10" s="54" t="str">
         <x:f>IF(F10&gt;=65,"明显有利",IF(F10&gt;=55,"偏有利",IF(F10&gt;=45,"中性",IF(F10&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="F11" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B11*('因子引擎'!$B$42-50))+(C11*('因子引擎'!$B$43-50))+(D11*('因子引擎'!$B$44-50))+(E11*('因子引擎'!$B$45-50)))/(ABS(B11)+ABS(C11)+ABS(D11)+ABS(E11))))</x:f>
-        <x:v>42.65079341806066</x:v>
+        <x:v>41.69186619733981</x:v>
       </x:c>
       <x:c r="G11" s="54" t="str">
         <x:f>IF(F11&gt;=65,"明显有利",IF(F11&gt;=55,"偏有利",IF(F11&gt;=45,"中性",IF(F11&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4538,7 +4538,7 @@
       </x:c>
       <x:c r="F12" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B12*('因子引擎'!$B$42-50))+(C12*('因子引擎'!$B$43-50))+(D12*('因子引擎'!$B$44-50))+(E12*('因子引擎'!$B$45-50)))/(ABS(B12)+ABS(C12)+ABS(D12)+ABS(E12))))</x:f>
-        <x:v>40.764492188550186</x:v>
+        <x:v>40.55900778411</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:f>IF(F12&gt;=65,"明显有利",IF(F12&gt;=55,"偏有利",IF(F12&gt;=45,"中性",IF(F12&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4572,11 +4572,11 @@
       </x:c>
       <x:c r="F13" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B13*('因子引擎'!$B$42-50))+(C13*('因子引擎'!$B$43-50))+(D13*('因子引擎'!$B$44-50))+(E13*('因子引擎'!$B$45-50)))/(ABS(B13)+ABS(C13)+ABS(D13)+ABS(E13))))</x:f>
-        <x:v>45.78407918986468</x:v>
+        <x:v>44.091854682710235</x:v>
       </x:c>
       <x:c r="G13" s="54" t="str">
         <x:f>IF(F13&gt;=65,"明显有利",IF(F13&gt;=55,"偏有利",IF(F13&gt;=45,"中性",IF(F13&gt;=35,"偏不利","明显不利"))))</x:f>
-        <x:v>中性</x:v>
+        <x:v>偏不利</x:v>
       </x:c>
       <x:c r="H13" s="54" t="str">
         <x:v>通胀与实物供需</x:v>
@@ -4606,7 +4606,7 @@
       </x:c>
       <x:c r="F14" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B14*('因子引擎'!$B$42-50))+(C14*('因子引擎'!$B$43-50))+(D14*('因子引擎'!$B$44-50))+(E14*('因子引擎'!$B$45-50)))/(ABS(B14)+ABS(C14)+ABS(D14)+ABS(E14))))</x:f>
-        <x:v>39.619700514709706</x:v>
+        <x:v>40.40427733166313</x:v>
       </x:c>
       <x:c r="G14" s="54" t="str">
         <x:f>IF(F14&gt;=65,"明显有利",IF(F14&gt;=55,"偏有利",IF(F14&gt;=45,"中性",IF(F14&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4640,7 +4640,7 @@
       </x:c>
       <x:c r="F15" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B15*('因子引擎'!$B$42-50))+(C15*('因子引擎'!$B$43-50))+(D15*('因子引擎'!$B$44-50))+(E15*('因子引擎'!$B$45-50)))/(ABS(B15)+ABS(C15)+ABS(D15)+ABS(E15))))</x:f>
-        <x:v>58.06173864479713</x:v>
+        <x:v>57.60145357885113</x:v>
       </x:c>
       <x:c r="G15" s="54" t="str">
         <x:f>IF(F15&gt;=65,"明显有利",IF(F15&gt;=55,"偏有利",IF(F15&gt;=45,"中性",IF(F15&gt;=35,"偏不利","明显不利"))))</x:f>
@@ -4848,7 +4848,7 @@
       </x:c>
       <x:c r="C6" s="58" t="n">
         <x:f>'因子引擎'!$B$43</x:f>
-        <x:v>49.95917150829179</x:v>
+        <x:v>47.08238984612924</x:v>
       </x:c>
       <x:c r="D6" s="58" t="n">
         <x:f>'因子引擎'!$B$44</x:f>
@@ -4860,27 +4860,27 @@
       </x:c>
       <x:c r="F6" s="58" t="n">
         <x:f>MIN(100,MAX(0,(35%*B6+35%*C6+30%*D6)*(0.75+0.5*E6/100)))</x:f>
-        <x:v>60.46469053817076</x:v>
+        <x:v>59.439028925534345</x:v>
       </x:c>
       <x:c r="G6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$6+(C6-50)*'风险资产'!$C$6+(D6-50)*'风险资产'!$D$6+(E6-50)*'风险资产'!$E$6)/(ABS('风险资产'!$B$6)+ABS('风险资产'!$C$6)+ABS('风险资产'!$D$6)+ABS('风险资产'!$E$6))))</x:f>
-        <x:v>40.78190734974757</x:v>
+        <x:v>41.43945744395615</x:v>
       </x:c>
       <x:c r="H6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$7+(C6-50)*'风险资产'!$C$7+(D6-50)*'风险资产'!$D$7+(E6-50)*'风险资产'!$E$7)/(ABS('风险资产'!$B$7)+ABS('风险资产'!$C$7)+ABS('风险资产'!$D$7)+ABS('风险资产'!$E$7))))</x:f>
-        <x:v>40.8430394023309</x:v>
+        <x:v>41.418395734763415</x:v>
       </x:c>
       <x:c r="I6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$9+(C6-50)*'风险资产'!$C$9+(D6-50)*'风险资产'!$D$9+(E6-50)*'风险资产'!$E$9)/(ABS('风险资产'!$B$9)+ABS('风险资产'!$C$9)+ABS('风险资产'!$D$9)+ABS('风险资产'!$E$9))))</x:f>
-        <x:v>42.38848017160706</x:v>
+        <x:v>42.81467004748299</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$11+(C6-50)*'风险资产'!$C$11+(D6-50)*'风险资产'!$D$11+(E6-50)*'风险资产'!$E$11)/(ABS('风险资产'!$B$11)+ABS('风险资产'!$C$11)+ABS('风险资产'!$D$11)+ABS('风险资产'!$E$11))))</x:f>
-        <x:v>42.65079341806066</x:v>
+        <x:v>41.69186619733981</x:v>
       </x:c>
       <x:c r="K6" s="58" t="n">
         <x:f>MAX(0,MIN(100,50+((B6-50)*'风险资产'!$B$15+(C6-50)*'风险资产'!$C$15+(D6-50)*'风险资产'!$D$15+(E6-50)*'风险资产'!$E$15)/(ABS('风险资产'!$B$15)+ABS('风险资产'!$C$15)+ABS('风险资产'!$D$15)+ABS('风险资产'!$E$15))))</x:f>
-        <x:v>58.06173864479713</x:v>
+        <x:v>57.60145357885113</x:v>
       </x:c>
       <x:c r="L6" s="54" t="str">
         <x:v>政策重定价与期限溢价偏紧，但信用/波动传导仅中等</x:v>
@@ -7250,7 +7250,7 @@
       </x:c>
       <x:c r="B12" s="88" t="n">
         <x:f>'因子引擎'!B47</x:f>
-        <x:v>60.46469053817076</x:v>
+        <x:v>59.439028925534345</x:v>
       </x:c>
       <x:c r="C12" s="88" t="str">
         <x:v>0-100</x:v>
@@ -7273,7 +7273,7 @@
       </x:c>
       <x:c r="B13" s="88" t="n">
         <x:f>MIN('风险资产'!F6:F15)</x:f>
-        <x:v>39.619700514709706</x:v>
+        <x:v>40.40427733166313</x:v>
       </x:c>
       <x:c r="C13" s="88" t="str">
         <x:v>0-100（并检查最大值）</x:v>

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="Rad0be1389c4444e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R19cb2779bc0341a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="Rd5fc300349654dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rcac17792e93a457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R3163750e9e4b4058"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R1a18343be299468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="R248bfebb55f84f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R5410161a47074dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R0019738f7888407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R0bdf3b04254c42d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R80045bdf28de4f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rb0b8e609ad994308"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R723e47dec0484099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Radb75dff58a94cec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7fc152484c0348e9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10f65c237f004f05"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cfa1b2389394023"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c67bcfdb4824de6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffa5d523652145d4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e6000da2d6f424a"/>
 </x:worksheet>
 </file>
 

--- a/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
+++ b/产业趋势研究&选股/君君美债利率模型_自动刷新/output/君君美债利率模型_最新.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R5410161a47074dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R0019738f7888407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R0bdf3b04254c42d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="R80045bdf28de4f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="Rb0b8e609ad994308"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R723e47dec0484099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Radb75dff58a94cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型总览" sheetId="1" r:id="R9e6ef10eaa1f4848"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子引擎" sheetId="2" r:id="R4576f8757fda428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险资产" sheetId="3" r:id="R68918f6eedd147d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景与阈值" sheetId="4" r:id="Rcaa151b866554e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="5" r:id="R01cb7d0763f648c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法与信源" sheetId="6" r:id="R958a7241d0e54935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计" sheetId="7" r:id="Rb2ab351b7a29486a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,7 +786,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10f65c237f004f05"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R421cac5bba5d44e3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -816,7 +816,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c67bcfdb4824de6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R84a99e138a1a49d4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2110,7 +2110,7 @@
     <x:mergeCell ref="A42:O44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e6000da2d6f424a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ece1b48f33495e"/>
 </x:worksheet>
 </file>
 
